--- a/src/resources/data/catalogInfo/excels/Drum_katalog_full.xlsx
+++ b/src/resources/data/catalogInfo/excels/Drum_katalog_full.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="BuÇalışmaKitabı" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\URETIM9\Desktop\katalog_upload\REFERANS CROSS NO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\URETIM9\Desktop\Projects\API_SCRAPE\src\resources\data\catalogInfo\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2FE3B1-AE7A-4C0A-A0F1-DF89B369B997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26B2EF8-A679-4404-8666-5D6B6CD506C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BULUNAMAYANLAR!$A$1:$A$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="1106">
   <si>
     <t>BREMBO</t>
   </si>
@@ -68,9 +68,6 @@
     <t>RAION stok kodu</t>
   </si>
   <si>
-    <t>_oem yatay</t>
-  </si>
-  <si>
     <t>24163</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>BSG 30-225-023</t>
   </si>
   <si>
-    <t>6008179, 1522611</t>
-  </si>
-  <si>
     <t>13280</t>
   </si>
   <si>
@@ -221,9 +215,6 @@
     <t>BSG 30-225-002</t>
   </si>
   <si>
-    <t>92VB1126BA, 6198026, 92VB1126RD</t>
-  </si>
-  <si>
     <t>13282</t>
   </si>
   <si>
@@ -251,9 +242,6 @@
     <t>BSG 30-225-001</t>
   </si>
   <si>
-    <t>92VB1126AA, 6464214</t>
-  </si>
-  <si>
     <t>13283</t>
   </si>
   <si>
@@ -278,9 +266,6 @@
     <t>BSG 30-225-024</t>
   </si>
   <si>
-    <t>96AA111395, 6560028, 6920711, 1011288, 7296355, 96AB1113, 96AB1113AB</t>
-  </si>
-  <si>
     <t>13284</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
     <t>94024600</t>
   </si>
   <si>
-    <t>4078769, 4041429, 4446218, 4519396, 3C111126AA</t>
-  </si>
-  <si>
     <t>13286</t>
   </si>
   <si>
@@ -350,9 +332,6 @@
     <t>94024800</t>
   </si>
   <si>
-    <t>YC1W1126ED, 4078770, 4446219, 4041430</t>
-  </si>
-  <si>
     <t>13290</t>
   </si>
   <si>
@@ -377,9 +356,6 @@
     <t>94024400</t>
   </si>
   <si>
-    <t>4467600, 4455981, 4367102, 4367103, 1334975, 1361304, 2T141126</t>
-  </si>
-  <si>
     <t>13289</t>
   </si>
   <si>
@@ -396,9 +372,6 @@
   </si>
   <si>
     <t>94022500</t>
-  </si>
-  <si>
-    <t>1M5W1113AA, 4186874, 4154689</t>
   </si>
   <si>
     <t>36020</t>
@@ -444,9 +417,6 @@
     <t>94006600</t>
   </si>
   <si>
-    <t>171501615, 171501615A, 171501615B, 171501615C, 191501615B</t>
-  </si>
-  <si>
     <t>25181</t>
   </si>
   <si>
@@ -498,9 +468,6 @@
     <t>BSG 40-225-007</t>
   </si>
   <si>
-    <t>0K60B26251, 0K60B26251A</t>
-  </si>
-  <si>
     <t>16183</t>
   </si>
   <si>
@@ -522,9 +489,6 @@
     <t>BSG 40-225-006</t>
   </si>
   <si>
-    <t>5276144102, 5276144101, 5276144500</t>
-  </si>
-  <si>
     <t>33149</t>
   </si>
   <si>
@@ -558,9 +522,6 @@
     <t>94014600</t>
   </si>
   <si>
-    <t>424738, 1306211080</t>
-  </si>
-  <si>
     <t>40217</t>
   </si>
   <si>
@@ -585,9 +546,6 @@
     <t>BSG 41-225-004</t>
   </si>
   <si>
-    <t>8942268291, 8970378130, 9030906160, 94226829, 94023920, 4294418, 568062, 94029151, 8979128660, 894226829151</t>
-  </si>
-  <si>
     <t>28324</t>
   </si>
   <si>
@@ -684,9 +642,6 @@
     <t>BSG 41-225-002</t>
   </si>
   <si>
-    <t>8973605060, 8980303850</t>
-  </si>
-  <si>
     <t>27381</t>
   </si>
   <si>
@@ -717,9 +672,6 @@
     <t>94022600</t>
   </si>
   <si>
-    <t>568063, 90538928</t>
-  </si>
-  <si>
     <t>27382</t>
   </si>
   <si>
@@ -753,9 +705,6 @@
     <t>BSG 65-225-002</t>
   </si>
   <si>
-    <t>568057, 568054, 90168958, 91024352, 96175281, 94608757, 568039, 90105445</t>
-  </si>
-  <si>
     <t>27383</t>
   </si>
   <si>
@@ -786,9 +735,6 @@
     <t>BSG 65-225-004</t>
   </si>
   <si>
-    <t>568058, 568053, 90086194, 90193915</t>
-  </si>
-  <si>
     <t>27384</t>
   </si>
   <si>
@@ -822,9 +768,6 @@
     <t>94009900</t>
   </si>
   <si>
-    <t>418117, 90007526, 90135504</t>
-  </si>
-  <si>
     <t>45387</t>
   </si>
   <si>
@@ -876,9 +819,6 @@
     <t>BSG 62-225-001</t>
   </si>
   <si>
-    <t>MB950951, MB534245, MB534235, MB193596</t>
-  </si>
-  <si>
     <t>45425H</t>
   </si>
   <si>
@@ -900,9 +840,6 @@
     <t>TFD-00523</t>
   </si>
   <si>
-    <t>P90005YP, P90005</t>
-  </si>
-  <si>
     <t>51435</t>
   </si>
   <si>
@@ -945,9 +882,6 @@
     <t>94031500</t>
   </si>
   <si>
-    <t>568066, 24444064</t>
-  </si>
-  <si>
     <t>27448</t>
   </si>
   <si>
@@ -981,9 +915,6 @@
     <t>94024100</t>
   </si>
   <si>
-    <t>418000, 9004416, 24401369</t>
-  </si>
-  <si>
     <t>18455</t>
   </si>
   <si>
@@ -993,9 +924,6 @@
     <t>TFD-00397</t>
   </si>
   <si>
-    <t>0K42A26251, 0K42A26251A</t>
-  </si>
-  <si>
     <t>26463</t>
   </si>
   <si>
@@ -1095,9 +1023,6 @@
     <t>BSG 40-225-001</t>
   </si>
   <si>
-    <t>584114F000, 584114F001</t>
-  </si>
-  <si>
     <t>25509</t>
   </si>
   <si>
@@ -1128,9 +1053,6 @@
     <t>94035300</t>
   </si>
   <si>
-    <t>MN102439, 4615A127, 4615A205</t>
-  </si>
-  <si>
     <t>16518</t>
   </si>
   <si>
@@ -1212,9 +1134,6 @@
     <t>94023800</t>
   </si>
   <si>
-    <t>6Q0609617, 6QE609617, 6QD609617</t>
-  </si>
-  <si>
     <t>13544</t>
   </si>
   <si>
@@ -1239,9 +1158,6 @@
     <t>94045600</t>
   </si>
   <si>
-    <t>EY161126AA, 1833868</t>
-  </si>
-  <si>
     <t>16561</t>
   </si>
   <si>
@@ -1269,9 +1185,6 @@
     <t>94035900</t>
   </si>
   <si>
-    <t>584111G000, 584111E000</t>
-  </si>
-  <si>
     <t>34565</t>
   </si>
   <si>
@@ -1299,9 +1212,6 @@
     <t>BSG 85-225-001</t>
   </si>
   <si>
-    <t>4243120250, 4243112130, 4243112180, 94852720</t>
-  </si>
-  <si>
     <t>40569</t>
   </si>
   <si>
@@ -1329,9 +1239,6 @@
     <t>94039400</t>
   </si>
   <si>
-    <t>8979480380, 8979480381, 8980618130, 8980618131, 8981364911, 97948038, 98061813</t>
-  </si>
-  <si>
     <t>36571</t>
   </si>
   <si>
@@ -1383,9 +1290,6 @@
     <t>BSG 75-225-004</t>
   </si>
   <si>
-    <t>432007212R, 432009234R</t>
-  </si>
-  <si>
     <t>33591</t>
   </si>
   <si>
@@ -1416,9 +1320,6 @@
     <t>94027200</t>
   </si>
   <si>
-    <t>51901443, 55701380, 55703043, 568270</t>
-  </si>
-  <si>
     <t>30579B</t>
   </si>
   <si>
@@ -1452,9 +1353,6 @@
     <t>07040390</t>
   </si>
   <si>
-    <t>424640, P7930010848</t>
-  </si>
-  <si>
     <t>33740</t>
   </si>
   <si>
@@ -1488,9 +1386,6 @@
     <t>94014000</t>
   </si>
   <si>
-    <t>7769850, 51816526, 60810025</t>
-  </si>
-  <si>
     <t>26747</t>
   </si>
   <si>
@@ -1536,9 +1431,6 @@
     <t>BSG 35-225-002</t>
   </si>
   <si>
-    <t>42610SR3000, 42610SR1000, 42610SE0000, 42610SE0010</t>
-  </si>
-  <si>
     <t>15702</t>
   </si>
   <si>
@@ -1650,9 +1542,6 @@
     <t>BSG 40-225-008</t>
   </si>
   <si>
-    <t>5841122000, 5841122010, 5841122020</t>
-  </si>
-  <si>
     <t>16707</t>
   </si>
   <si>
@@ -1677,9 +1566,6 @@
     <t>RAI-KD02020</t>
   </si>
   <si>
-    <t>5841125010, 5841125100</t>
-  </si>
-  <si>
     <t>16708</t>
   </si>
   <si>
@@ -1722,9 +1608,6 @@
     <t>BSG 40-225-011</t>
   </si>
   <si>
-    <t>584111C000, 584111C010</t>
-  </si>
-  <si>
     <t>16710</t>
   </si>
   <si>
@@ -1788,9 +1671,6 @@
     <t>BSG 55-225-003</t>
   </si>
   <si>
-    <t>0S08326251B, 0S08326251C, S08326251, S08326251A, S08326251B, S08326251C</t>
-  </si>
-  <si>
     <t>22712</t>
   </si>
   <si>
@@ -1815,9 +1695,6 @@
     <t>BSG 55-225-001</t>
   </si>
   <si>
-    <t>B45526251, B45526251A, B45526251B</t>
-  </si>
-  <si>
     <t>22713</t>
   </si>
   <si>
@@ -1842,9 +1719,6 @@
     <t>BSG 55-225-004</t>
   </si>
   <si>
-    <t>B59626251, B59626251A, B59626251B, B59626251C, BW7Y26251, DN2026251, F2C612448</t>
-  </si>
-  <si>
     <t>22714</t>
   </si>
   <si>
@@ -1857,9 +1731,6 @@
     <t>BSG 55-225-002</t>
   </si>
   <si>
-    <t>GJ2126251, GJ2126251A, GJ2126251B, GJ2126251AB</t>
-  </si>
-  <si>
     <t>26715</t>
   </si>
   <si>
@@ -1887,9 +1758,6 @@
     <t>94036700</t>
   </si>
   <si>
-    <t>432062S600, 432060W710, 43206VE860, 43206VM30B, 440101W610</t>
-  </si>
-  <si>
     <t>32716</t>
   </si>
   <si>
@@ -1911,9 +1779,6 @@
     <t>BSG 83-225-002</t>
   </si>
   <si>
-    <t>4351177E00, 4351177EA0</t>
-  </si>
-  <si>
     <t>34717</t>
   </si>
   <si>
@@ -1935,9 +1800,6 @@
     <t>BSG 85-225-005</t>
   </si>
   <si>
-    <t>4243135151, 4243135150, 4243135120, 4243135080</t>
-  </si>
-  <si>
     <t>34718</t>
   </si>
   <si>
@@ -1962,9 +1824,6 @@
     <t>94038600</t>
   </si>
   <si>
-    <t>424310K080, 424310K090, 424310K220</t>
-  </si>
-  <si>
     <t>34719</t>
   </si>
   <si>
@@ -1992,9 +1851,6 @@
     <t>94038800</t>
   </si>
   <si>
-    <t>424310K120, 424310K130, 424310K250</t>
-  </si>
-  <si>
     <t>34720</t>
   </si>
   <si>
@@ -2016,9 +1872,6 @@
     <t>94029300</t>
   </si>
   <si>
-    <t>4243152020, 4243152021</t>
-  </si>
-  <si>
     <t>34722</t>
   </si>
   <si>
@@ -2157,9 +2010,6 @@
     <t>BSG 83-225-001</t>
   </si>
   <si>
-    <t>4351160G00, 4351160G10, 4351160G10000</t>
-  </si>
-  <si>
     <t>32735</t>
   </si>
   <si>
@@ -2190,9 +2040,6 @@
     <t>94026500</t>
   </si>
   <si>
-    <t>424748, 424310H010, LK3502111</t>
-  </si>
-  <si>
     <t>34739</t>
   </si>
   <si>
@@ -2256,9 +2103,6 @@
     <t>94024200</t>
   </si>
   <si>
-    <t>418001, 9196290, 9156697, 9004417</t>
-  </si>
-  <si>
     <t>30777</t>
   </si>
   <si>
@@ -2283,9 +2127,6 @@
     <t>94013700</t>
   </si>
   <si>
-    <t>7700710511, 8200137104, 8200028861</t>
-  </si>
-  <si>
     <t>33783</t>
   </si>
   <si>
@@ -2301,9 +2142,6 @@
     <t>94020000</t>
   </si>
   <si>
-    <t>5923606, 4379680</t>
-  </si>
-  <si>
     <t>16789</t>
   </si>
   <si>
@@ -2328,9 +2166,6 @@
     <t>94034900</t>
   </si>
   <si>
-    <t>5841117200, 5841117100, 5841129A00, 5841129000, 5275129000</t>
-  </si>
-  <si>
     <t>16790</t>
   </si>
   <si>
@@ -2349,9 +2184,6 @@
     <t>94046700</t>
   </si>
   <si>
-    <t>584111R000, 584110U000, 584110U000DS</t>
-  </si>
-  <si>
     <t>42804</t>
   </si>
   <si>
@@ -2406,9 +2238,6 @@
     <t>BSG 75-225-005</t>
   </si>
   <si>
-    <t>7700685473, 7700752363, 7700783030, 7701463277</t>
-  </si>
-  <si>
     <t>31820</t>
   </si>
   <si>
@@ -2448,9 +2277,6 @@
     <t>94014800</t>
   </si>
   <si>
-    <t>46819776, 51863509, 51863510, 51900802, 7599325, 7750119</t>
-  </si>
-  <si>
     <t>29825</t>
   </si>
   <si>
@@ -2463,9 +2289,6 @@
     <t>94014200</t>
   </si>
   <si>
-    <t>424735, 424744, 95659622</t>
-  </si>
-  <si>
     <t>29826</t>
   </si>
   <si>
@@ -2478,9 +2301,6 @@
     <t>94028200</t>
   </si>
   <si>
-    <t>424741, 424745, 424747</t>
-  </si>
-  <si>
     <t>33827</t>
   </si>
   <si>
@@ -2511,9 +2331,6 @@
     <t>RAI-KD02041</t>
   </si>
   <si>
-    <t>584114E000, OEK584114E000</t>
-  </si>
-  <si>
     <t>33976</t>
   </si>
   <si>
@@ -2529,18 +2346,12 @@
     <t>94010200</t>
   </si>
   <si>
-    <t>4449694, 424722, ZF4449694</t>
-  </si>
-  <si>
     <t>33987</t>
   </si>
   <si>
     <t>14.3157.20</t>
   </si>
   <si>
-    <t>5923924, JA16520152</t>
-  </si>
-  <si>
     <t>28988</t>
   </si>
   <si>
@@ -2553,9 +2364,6 @@
     <t>94026600</t>
   </si>
   <si>
-    <t>424746, 424749, 424752</t>
-  </si>
-  <si>
     <t>45387H</t>
   </si>
   <si>
@@ -2574,9 +2382,6 @@
     <t>BDK300 33392</t>
   </si>
   <si>
-    <t>51860868, 51864509, 51898123, 52015297, 568002, 95515120</t>
-  </si>
-  <si>
     <t>30997</t>
   </si>
   <si>
@@ -2586,18 +2391,12 @@
     <t>07050096</t>
   </si>
   <si>
-    <t>432004334R, 432007629R, 432000978R</t>
-  </si>
-  <si>
     <t>161065</t>
   </si>
   <si>
     <t>07050084</t>
   </si>
   <si>
-    <t>584111S100, 584111S000</t>
-  </si>
-  <si>
     <t>291066</t>
   </si>
   <si>
@@ -2652,9 +2451,6 @@
     <t>14.4739.10</t>
   </si>
   <si>
-    <t>4243135060, 4243135090</t>
-  </si>
-  <si>
     <t>251075</t>
   </si>
   <si>
@@ -2679,9 +2475,6 @@
     <t>94037800</t>
   </si>
   <si>
-    <t>4351165D00, 4351167D00, 4351182A00, 4351165D10</t>
-  </si>
-  <si>
     <t>191082</t>
   </si>
   <si>
@@ -2697,9 +2490,6 @@
     <t>94015600</t>
   </si>
   <si>
-    <t>21080350207000, 21083502070, 2108350207</t>
-  </si>
-  <si>
     <t>341083</t>
   </si>
   <si>
@@ -2709,9 +2499,6 @@
     <t>341084</t>
   </si>
   <si>
-    <t>4351236190, 4351236191</t>
-  </si>
-  <si>
     <t>131085</t>
   </si>
   <si>
@@ -2724,9 +2511,6 @@
     <t>BSG 30-225-005</t>
   </si>
   <si>
-    <t>4146930, 4540218, 1C1W1126AD, 1C1W1126AE, 1C1W1126AB</t>
-  </si>
-  <si>
     <t>131086</t>
   </si>
   <si>
@@ -2736,18 +2520,12 @@
     <t>07050093</t>
   </si>
   <si>
-    <t>R2X61126AAN, R2X61126AA, 2660440</t>
-  </si>
-  <si>
     <t>341087</t>
   </si>
   <si>
     <t>14.E277.10</t>
   </si>
   <si>
-    <t>424310D100, 424310D080, 4243152070</t>
-  </si>
-  <si>
     <t>30997B</t>
   </si>
   <si>
@@ -2757,33 +2535,21 @@
     <t>511089</t>
   </si>
   <si>
-    <t>42431B1011, 42431B1020, 42431B1020000, 42431B1021, 42431B2040, 42431B1020, 42431B1011, 42431B1021, 42431B2040</t>
-  </si>
-  <si>
     <t>261090</t>
   </si>
   <si>
-    <t>4320608G11, 43206VG300, 43206VM00B</t>
-  </si>
-  <si>
     <t>261091</t>
   </si>
   <si>
     <t>94026900</t>
   </si>
   <si>
-    <t>432064M000, 432064M400, 432064M401, 432064Z801, 432066N000</t>
-  </si>
-  <si>
     <t>341092</t>
   </si>
   <si>
     <t>94045200</t>
   </si>
   <si>
-    <t>424310D030000, 424310D030</t>
-  </si>
-  <si>
     <t>TEXTAR</t>
   </si>
   <si>
@@ -2827,13 +2593,775 @@
   </si>
   <si>
     <t>OE</t>
+  </si>
+  <si>
+    <t>DB4143</t>
+  </si>
+  <si>
+    <t>6008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1522611</t>
+  </si>
+  <si>
+    <t>92VB1126BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6198026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 92VB1126RD</t>
+  </si>
+  <si>
+    <t>92VB1126AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6464214</t>
+  </si>
+  <si>
+    <t>96AA111395</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6920711</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 96AB1113</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 96AB1113AB</t>
+  </si>
+  <si>
+    <t>4078769</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4041429</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4446218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3C111126AA</t>
+  </si>
+  <si>
+    <t>YC1W1126ED</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4078770</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4446219</t>
+  </si>
+  <si>
+    <t>4467600</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4455981</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4367102</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2T141126</t>
+  </si>
+  <si>
+    <t>1M5W1113AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4154689</t>
+  </si>
+  <si>
+    <t>171501615</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 171501615A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 171501615B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 171501615C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 191501615B</t>
+  </si>
+  <si>
+    <t>0K60B26251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0K60B26251A</t>
+  </si>
+  <si>
+    <t>5276144102</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5276144101</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5276144500</t>
+  </si>
+  <si>
+    <t>424738</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1306211080</t>
+  </si>
+  <si>
+    <t>8942268291</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8970378130</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9030906160</t>
+  </si>
+  <si>
+    <t>8973605060</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8980303850</t>
+  </si>
+  <si>
+    <t>568063</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 90538928</t>
+  </si>
+  <si>
+    <t>568057</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 90168958</t>
+  </si>
+  <si>
+    <t>568058</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 568053</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 90086194</t>
+  </si>
+  <si>
+    <t>418117</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 90007526</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 90135504</t>
+  </si>
+  <si>
+    <t>3757089</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 921750</t>
+  </si>
+  <si>
+    <t>28288</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 18019</t>
+  </si>
+  <si>
+    <t>MB950951</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MB534245</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MB534235</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MB193596</t>
+  </si>
+  <si>
+    <t>P90005YP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P90005</t>
+  </si>
+  <si>
+    <t>568066</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 24444064</t>
+  </si>
+  <si>
+    <t>418000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9004416</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 24401369</t>
+  </si>
+  <si>
+    <t>0K42A26251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0K42A26251A</t>
+  </si>
+  <si>
+    <t>584114F000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 584114F001</t>
+  </si>
+  <si>
+    <t>MN102439</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4615A127</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4615A205</t>
+  </si>
+  <si>
+    <t>6Q0609617</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6QE609617</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6QD609617</t>
+  </si>
+  <si>
+    <t>EY161126AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1833868</t>
+  </si>
+  <si>
+    <t>584111G000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 584111E000</t>
+  </si>
+  <si>
+    <t>4243120250</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243112130</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243112180</t>
+  </si>
+  <si>
+    <t>8979480380</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8979480381</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8980618130</t>
+  </si>
+  <si>
+    <t>432007212R</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432009234R</t>
+  </si>
+  <si>
+    <t>51901443</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 55701380</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 55703043</t>
+  </si>
+  <si>
+    <t>424640</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P7930010848</t>
+  </si>
+  <si>
+    <t>7769850</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51816526</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 60810025</t>
+  </si>
+  <si>
+    <t>42610SR3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42610SR1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42610SE0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42610SE0010</t>
+  </si>
+  <si>
+    <t>5841122000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5841122010</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5841122020</t>
+  </si>
+  <si>
+    <t>5841125010</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5841125100</t>
+  </si>
+  <si>
+    <t>584111C000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 584111C010</t>
+  </si>
+  <si>
+    <t>0S08326251B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0S08326251C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S08326251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S08326251A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S08326251B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S08326251C</t>
+  </si>
+  <si>
+    <t>B45526251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B45526251A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B45526251B</t>
+  </si>
+  <si>
+    <t>B59626251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B59626251A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B59626251B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B59626251C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BW7Y26251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DN2026251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F2C612448</t>
+  </si>
+  <si>
+    <t>GJ2126251</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GJ2126251A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GJ2126251B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GJ2126251AB</t>
+  </si>
+  <si>
+    <t>432062S600</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432060W710</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 43206VE860</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 43206VM30B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 440101W610</t>
+  </si>
+  <si>
+    <t>4351177E00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351177EA0</t>
+  </si>
+  <si>
+    <t>4243135151</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243135150</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243135120</t>
+  </si>
+  <si>
+    <t>424310K080</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310K090</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310K220</t>
+  </si>
+  <si>
+    <t>424310K120</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310K130</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310K250</t>
+  </si>
+  <si>
+    <t>4243152020</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243152021</t>
+  </si>
+  <si>
+    <t>4351160G00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351160G10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351160G10000</t>
+  </si>
+  <si>
+    <t>424748</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310H010</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LK3502111</t>
+  </si>
+  <si>
+    <t>418001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9196290</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9156697</t>
+  </si>
+  <si>
+    <t>7700710511</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8200137104</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8200028861</t>
+  </si>
+  <si>
+    <t>5923606</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4379680</t>
+  </si>
+  <si>
+    <t>5841117200</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5841117100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5841129A00</t>
+  </si>
+  <si>
+    <t>584111R000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 584110U000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 584110U000DS</t>
+  </si>
+  <si>
+    <t>7700685473</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7700752363</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7700783030</t>
+  </si>
+  <si>
+    <t>46819776</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51863509</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51863510</t>
+  </si>
+  <si>
+    <t>424735</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 95659622</t>
+  </si>
+  <si>
+    <t>424741</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424745</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424747</t>
+  </si>
+  <si>
+    <t>584114E000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OEK584114E000</t>
+  </si>
+  <si>
+    <t>4449694</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424722</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ZF4449694</t>
+  </si>
+  <si>
+    <t>5923924</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JA16520152</t>
+  </si>
+  <si>
+    <t>424746</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424749</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424752</t>
+  </si>
+  <si>
+    <t>51860868</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51864509</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 51898123</t>
+  </si>
+  <si>
+    <t>432004334R</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432007629R</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432000978R</t>
+  </si>
+  <si>
+    <t>584111S100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 584111S000</t>
+  </si>
+  <si>
+    <t>3302350207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 33023502070</t>
+  </si>
+  <si>
+    <t>8970339891</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8941010571</t>
+  </si>
+  <si>
+    <t>8973341070AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8973341070</t>
+  </si>
+  <si>
+    <t>4243135060</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243135090</t>
+  </si>
+  <si>
+    <t>4351165D00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351167D00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351182A00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351165D10</t>
+  </si>
+  <si>
+    <t>21080350207000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 21083502070</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2108350207</t>
+  </si>
+  <si>
+    <t>4351236190</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4351236191</t>
+  </si>
+  <si>
+    <t>4146930</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4540218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1C1W1126AD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1C1W1126AE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1C1W1126AB</t>
+  </si>
+  <si>
+    <t>R2X61126AAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R2X61126AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2660440</t>
+  </si>
+  <si>
+    <t>424310D100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310D080</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4243152070</t>
+  </si>
+  <si>
+    <t>42431B1011</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42431B1020</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42431B1020000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42431B1021</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42431B2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 42431B1011</t>
+  </si>
+  <si>
+    <t>4320608G11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 43206VG300</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 43206VM00B</t>
+  </si>
+  <si>
+    <t>432064M000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432064M400</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432064M401</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432064Z801</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 432066N000</t>
+  </si>
+  <si>
+    <t>424310D030000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 424310D030</t>
+  </si>
+  <si>
+    <t>894226829151</t>
+  </si>
+  <si>
+    <t>OE_1</t>
+  </si>
+  <si>
+    <t>OE_2</t>
+  </si>
+  <si>
+    <t>OE_3</t>
+  </si>
+  <si>
+    <t>OE_4</t>
+  </si>
+  <si>
+    <t>OE_5</t>
+  </si>
+  <si>
+    <t>OE_6</t>
+  </si>
+  <si>
+    <t>OE_7</t>
+  </si>
+  <si>
+    <t>OE_8</t>
+  </si>
+  <si>
+    <t>OE_9</t>
+  </si>
+  <si>
+    <t>OE_10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2884,6 +3412,12 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2911,7 +3445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2983,6 +3517,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3298,7 +3836,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sayfa1"/>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:AC128"/>
   <sheetFormatPr defaultColWidth="22.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -3311,19 +3849,28 @@
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.88671875" customWidth="1"/>
-    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="103.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.88671875" customWidth="1"/>
+    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>916</v>
+        <v>838</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3338,13 +3885,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>927</v>
+        <v>849</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>920</v>
+        <v>842</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -3353,3112 +3900,4034 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="T1" s="27" t="s">
+        <v>1096</v>
+      </c>
+      <c r="U1" s="27" t="s">
+        <v>1097</v>
+      </c>
+      <c r="V1" s="27" t="s">
+        <v>1098</v>
+      </c>
+      <c r="W1" s="27" t="s">
+        <v>1099</v>
+      </c>
+      <c r="X1" s="27" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Y1" s="27" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Z1" s="27" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AA1" s="27" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AB1" s="27" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AC1" s="27" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="21"/>
+      <c r="N4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="21"/>
+      <c r="N6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="T6" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>853</v>
+      </c>
+      <c r="U7" s="28" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>844</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" s="21"/>
+      <c r="N8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="T9" s="18" t="s">
+        <v>855</v>
+      </c>
+      <c r="U9" s="28" t="s">
+        <v>856</v>
+      </c>
+      <c r="V9" s="28" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="T10" s="18" t="s">
+        <v>858</v>
+      </c>
+      <c r="U10" s="28" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q11" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>860</v>
+      </c>
+      <c r="U11" s="28" t="s">
+        <v>861</v>
+      </c>
+      <c r="V11" s="28" t="s">
+        <v>862</v>
+      </c>
+      <c r="W11">
+        <v>1011288</v>
+      </c>
+      <c r="X11">
+        <v>7296355</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>863</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="T12" s="21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18" t="s">
+        <v>865</v>
+      </c>
+      <c r="U13" s="28" t="s">
+        <v>866</v>
+      </c>
+      <c r="V13" s="28" t="s">
+        <v>867</v>
+      </c>
+      <c r="W13">
+        <v>4519396</v>
+      </c>
+      <c r="X13" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18" t="s">
+        <v>869</v>
+      </c>
+      <c r="U14" s="28" t="s">
+        <v>870</v>
+      </c>
+      <c r="V14" s="28" t="s">
+        <v>871</v>
+      </c>
+      <c r="W14">
+        <v>4041430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18" t="s">
+        <v>872</v>
+      </c>
+      <c r="U15" s="28" t="s">
+        <v>873</v>
+      </c>
+      <c r="V15" s="28" t="s">
+        <v>874</v>
+      </c>
+      <c r="W15">
+        <v>4367103</v>
+      </c>
+      <c r="X15">
+        <v>1334975</v>
+      </c>
+      <c r="Y15">
+        <v>1361304</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18" t="s">
+        <v>876</v>
+      </c>
+      <c r="U16" s="28" t="s">
+        <v>877</v>
+      </c>
+      <c r="V16" s="28" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="R17" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18" t="s">
+        <v>879</v>
+      </c>
+      <c r="U17" s="28" t="s">
+        <v>880</v>
+      </c>
+      <c r="V17" s="28" t="s">
+        <v>881</v>
+      </c>
+      <c r="W17" t="s">
+        <v>882</v>
+      </c>
+      <c r="X17" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P19" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>884</v>
+      </c>
+      <c r="U19" s="28" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="T20" s="18" t="s">
+        <v>886</v>
+      </c>
+      <c r="U20" s="28" t="s">
+        <v>887</v>
+      </c>
+      <c r="V20" s="28" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="R21" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18" t="s">
+        <v>889</v>
+      </c>
+      <c r="U21" s="28" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="P22" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="T22" s="18" t="s">
+        <v>891</v>
+      </c>
+      <c r="U22" s="28" t="s">
+        <v>892</v>
+      </c>
+      <c r="V22" s="28" t="s">
+        <v>893</v>
+      </c>
+      <c r="W22">
+        <v>94226829</v>
+      </c>
+      <c r="X22">
+        <v>94023920</v>
+      </c>
+      <c r="Y22">
+        <v>4294418</v>
+      </c>
+      <c r="Z22">
+        <v>568062</v>
+      </c>
+      <c r="AA22">
+        <v>94029151</v>
+      </c>
+      <c r="AB22">
+        <v>8979128660</v>
+      </c>
+      <c r="AC22" s="28" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="R23" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" t="s">
+        <v>852</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="T24" s="18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="P25" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="T25" s="18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="P26" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="T26" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="U26" s="28" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="L27" t="s">
+        <v>207</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="R27" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18" t="s">
+        <v>896</v>
+      </c>
+      <c r="U27" s="28" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q28" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>898</v>
+      </c>
+      <c r="U28" s="28" t="s">
+        <v>899</v>
+      </c>
+      <c r="V28" s="28" t="s">
+        <v>900</v>
+      </c>
+      <c r="W28">
+        <v>91024352</v>
+      </c>
+      <c r="X28">
+        <v>96175281</v>
+      </c>
+      <c r="Y28">
+        <v>94608757</v>
+      </c>
+      <c r="Z28">
+        <v>568039</v>
+      </c>
+      <c r="AA28">
+        <v>90105445</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q29" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="T29" s="18" t="s">
+        <v>901</v>
+      </c>
+      <c r="U29" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="V29" s="28" t="s">
+        <v>903</v>
+      </c>
+      <c r="W29">
+        <v>90193915</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="O30" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q30" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="R30" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18" t="s">
+        <v>904</v>
+      </c>
+      <c r="U30" s="28" t="s">
+        <v>905</v>
+      </c>
+      <c r="V30" s="28" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="M31" s="22"/>
+      <c r="N31" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="T31" s="21" t="s">
+        <v>907</v>
+      </c>
+      <c r="U31" s="28" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="22"/>
+      <c r="N32" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="T32" s="21" t="s">
+        <v>909</v>
+      </c>
+      <c r="U32" s="28" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q33" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="T33" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="U33" s="28" t="s">
+        <v>912</v>
+      </c>
+      <c r="V33" s="28" t="s">
+        <v>913</v>
+      </c>
+      <c r="W33" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="M34" s="22"/>
+      <c r="N34" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="T34" s="21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="T35" s="18" t="s">
+        <v>915</v>
+      </c>
+      <c r="U35" s="28" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="N36" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="T36" s="18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="O37" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q37" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="R37" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18" t="s">
+        <v>917</v>
+      </c>
+      <c r="U37" s="28" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="N38" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q38" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="R38" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18" t="s">
+        <v>919</v>
+      </c>
+      <c r="U38" s="28" t="s">
+        <v>920</v>
+      </c>
+      <c r="V38" s="28" t="s">
         <v>921</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>918</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F39" s="21"/>
+      <c r="L39" t="s">
+        <v>293</v>
+      </c>
+      <c r="M39" s="21"/>
+      <c r="N39" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="S39" s="23" t="s">
+        <v>846</v>
+      </c>
+      <c r="T39" s="18" t="s">
+        <v>922</v>
+      </c>
+      <c r="U39" s="28" t="s">
         <v>923</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="S6" s="21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>922</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="S8" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="S10" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="S12" s="21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q14" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q15" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q16" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="N17" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O17" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="P17" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q17" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="O18" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="P18" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="S18" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="N19" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="O19" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="P19" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="S19" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="P20" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="S20" s="18" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q21" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="O22" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="P22" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="S22" s="18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="N23" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q23" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="M24" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="P24" s="16" t="s">
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="T40" s="18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="M41" s="22"/>
+      <c r="N41" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="T41" s="22"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="L42" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="T42" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="O43" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q43" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="T43" s="18" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="L44" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="O44" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="P44" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q44" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="T44" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="U44" s="28" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="N45" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="O45" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q45" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="R45" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18" t="s">
+        <v>926</v>
+      </c>
+      <c r="U45" s="28" t="s">
+        <v>927</v>
+      </c>
+      <c r="V45" s="28" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="L46" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="N46" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="P46" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q46" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="T46" s="18" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="N47" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="T47" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="M48" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="N48" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q48" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="R48" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="S48" s="18"/>
+      <c r="T48" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="U48" s="28" t="s">
+        <v>930</v>
+      </c>
+      <c r="V48" s="28" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="M49" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="N49" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="O49" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q49" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18" t="s">
+        <v>932</v>
+      </c>
+      <c r="U49" s="28" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="M50" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="N50" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="O50" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="P50" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q50" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="R50" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="S50" s="18"/>
+      <c r="T50" s="18" t="s">
+        <v>934</v>
+      </c>
+      <c r="U50" s="28" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="M51" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="O51" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="P51" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q51" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="T51" s="18" t="s">
+        <v>936</v>
+      </c>
+      <c r="U51" s="28" t="s">
+        <v>937</v>
+      </c>
+      <c r="V51" s="28" t="s">
+        <v>938</v>
+      </c>
+      <c r="W51">
+        <v>94852720</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="N52" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="S24" s="18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="O25" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="P25" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="S25" s="18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="N26" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="O26" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="S26" s="18" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="N27" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q27" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="N28" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="S28" s="18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="N29" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="P29" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="S29" s="18" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="N30" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="P30" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q30" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="L31" s="22"/>
-      <c r="M31" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="S31" s="21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="L32" s="22"/>
-      <c r="M32" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="S32" s="21" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="M33" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="N33" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="O33" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="P33" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="S33" s="18" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="L34" s="22"/>
-      <c r="M34" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="S34" s="21" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="M35" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="S35" s="18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="M36" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="O36" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S36" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="M37" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="N37" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="P37" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q37" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="M38" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="N38" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="P38" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q38" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F39" s="21"/>
-      <c r="L39" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="M39" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="R39" s="23" t="s">
-        <v>924</v>
-      </c>
-      <c r="S39" s="18" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="M40" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="O40" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="S40" s="18" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="L41" s="22"/>
-      <c r="M41" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="S41" s="22"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="K42" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="M42" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="S42" s="18" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="L43" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="M43" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="N43" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="P43" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="S43" s="18" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="L44" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="M44" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="N44" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="O44" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="P44" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="S44" s="18" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="L45" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="M45" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="N45" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="O45" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="P45" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q45" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="L46" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="M46" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="O46" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="P46" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="S46" s="18" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="L47" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="M47" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="S47" s="18" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="L48" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="M48" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="N48" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="P48" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q48" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="L49" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="M49" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="N49" s="14" t="s">
+      <c r="P52" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="P49" s="16" t="s">
+      <c r="Q52" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="Q49" s="17" t="s">
+      <c r="R52" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18" t="s">
+      <c r="S52" s="18"/>
+      <c r="T52" s="18" t="s">
+        <v>939</v>
+      </c>
+      <c r="U52" s="28" t="s">
+        <v>940</v>
+      </c>
+      <c r="V52" s="28" t="s">
+        <v>941</v>
+      </c>
+      <c r="W52">
+        <v>8980618131</v>
+      </c>
+      <c r="X52">
+        <v>8981364911</v>
+      </c>
+      <c r="Y52">
+        <v>97948038</v>
+      </c>
+      <c r="Z52">
+        <v>98061813</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="D53" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="L50" s="12" t="s">
+      <c r="F53" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="M50" s="13" t="s">
+      <c r="K53" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="N50" s="14" t="s">
+      <c r="L53" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="O50" s="15" t="s">
+      <c r="M53" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q53" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="P50" s="16" t="s">
+      <c r="R53" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="Q50" s="17" t="s">
+      <c r="S53" s="18"/>
+      <c r="T53" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18" t="s">
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="K54" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="L54" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="M54" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="O54" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="L51" s="12" t="s">
+      <c r="Q54" s="16" t="s">
         <v>416</v>
       </c>
-      <c r="N51" s="14" t="s">
+      <c r="T54" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="U54" s="28" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="O51" s="15" t="s">
+      <c r="B55" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="P51" s="16" t="s">
+      <c r="C55" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="S51" s="18" t="s">
+      <c r="D55" s="5" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="E55" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="K55" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="L55" s="18" t="s">
         <v>423</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="M55" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="O55" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="Q55" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="L52" s="12" t="s">
+      <c r="R55" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="M52" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="O52" s="15" t="s">
+      <c r="S55" s="18"/>
+      <c r="T55" s="18" t="s">
+        <v>944</v>
+      </c>
+      <c r="U55" s="28" t="s">
+        <v>945</v>
+      </c>
+      <c r="V55" s="28" t="s">
+        <v>946</v>
+      </c>
+      <c r="W55">
+        <v>568270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="P52" s="16" t="s">
+      <c r="C56" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="K56" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="L56" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="R52" s="18"/>
-      <c r="S52" s="18" t="s">
+      <c r="M56" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="N56" s="13" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="O56" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="R56" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="S56" s="18"/>
+      <c r="T56" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="U56" s="28" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="C57" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K57" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="L53" s="12" t="s">
+      <c r="L57" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="P53" s="16" t="s">
+      <c r="M57" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="T57" s="18" t="s">
+        <v>947</v>
+      </c>
+      <c r="U57" s="28" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="Q53" s="17" t="s">
+      <c r="B58" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="R53" s="18"/>
-      <c r="S53" s="18" t="s">
+      <c r="C58" s="4" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+      <c r="D58" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="E58" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="J58" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K58" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="L54" s="12" t="s">
+      <c r="L58" s="18" t="s">
         <v>445</v>
       </c>
-      <c r="N54" s="14" t="s">
+      <c r="M58" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="O58" s="14" t="s">
         <v>446</v>
       </c>
-      <c r="P54" s="16" t="s">
+      <c r="Q58" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="S54" s="18" t="s">
+      <c r="R58" s="17" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="S58" s="18"/>
+      <c r="T58" s="18" t="s">
+        <v>949</v>
+      </c>
+      <c r="U58" s="28" t="s">
+        <v>950</v>
+      </c>
+      <c r="V58" s="28" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="K59" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="L59" s="18" t="s">
         <v>451</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="M59" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="P59" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="Q59" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="R59" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="L55" s="12" t="s">
+      <c r="S59" s="18"/>
+      <c r="T59" s="18" t="s">
         <v>455</v>
       </c>
-      <c r="N55" s="14" t="s">
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="P55" s="16" t="s">
+      <c r="C60" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="Q55" s="17" t="s">
+      <c r="D60" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="R55" s="18"/>
-      <c r="S55" s="18" t="s">
+      <c r="E60" s="6" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="J60" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="K56" s="11" t="s">
+      <c r="L60" t="s">
         <v>461</v>
       </c>
-      <c r="L56" s="12" t="s">
+      <c r="M60" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="P60" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="M56" s="13" t="s">
+      <c r="Q60" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="N56" s="14" t="s">
+      <c r="T60" s="18" t="s">
+        <v>952</v>
+      </c>
+      <c r="U60" s="28" t="s">
+        <v>953</v>
+      </c>
+      <c r="V60" s="28" t="s">
+        <v>954</v>
+      </c>
+      <c r="W60" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="Q56" s="17" t="s">
+      <c r="E61" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="R56" s="18"/>
-      <c r="S56" s="18" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="K61" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="L61" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="M61" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="P61" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="Q61" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="L57" s="12" t="s">
+      <c r="R61" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="S57" s="18" t="s">
+      <c r="S61" s="18"/>
+      <c r="T61" s="18" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="K62" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="L62" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="M62" s="20" t="s">
+        <v>474</v>
+      </c>
+      <c r="P62" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="T62" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="J58" s="10" t="s">
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K63" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="L58" s="12" t="s">
+      <c r="L63" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="N58" s="14" t="s">
+      <c r="M63" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="P63" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="P58" s="16" t="s">
+      <c r="Q63" s="16" t="s">
         <v>481</v>
       </c>
-      <c r="Q58" s="17" t="s">
+      <c r="T63" s="18" t="s">
         <v>482</v>
       </c>
-      <c r="R58" s="18"/>
-      <c r="S58" s="18" t="s">
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="C64" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="D64" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="L59" s="12" t="s">
+      <c r="F64" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="O59" s="15" t="s">
+      <c r="J64" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="P59" s="16" t="s">
+      <c r="K64" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="Q59" s="17" t="s">
+      <c r="L64" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="R59" s="18"/>
-      <c r="S59" s="18" t="s">
+      <c r="M64" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="P64" s="15" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="Q64" s="16" t="s">
         <v>491</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="T64" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="D60" s="5" t="s">
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="J60" s="10" t="s">
+      <c r="D65" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E65" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="L60" s="12" t="s">
+      <c r="J65" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="O60" s="15" t="s">
+      <c r="L65" t="s">
         <v>497</v>
       </c>
-      <c r="P60" s="16" t="s">
+      <c r="M65" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="O65" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="S60" s="18" t="s">
+      <c r="P65" s="15" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="Q65" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="T65" s="18" t="s">
+        <v>956</v>
+      </c>
+      <c r="U65" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="V65" s="28" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="B66" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="L61" s="12" t="s">
+      <c r="C66" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="O61" s="15" t="s">
+      <c r="D66" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="P61" s="16" t="s">
+      <c r="F66" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="Q61" s="17" t="s">
+      <c r="K66" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="R61" s="18"/>
-      <c r="S61" s="18" t="s">
+      <c r="L66" s="18" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="M66" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="P66" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="T66" s="18" t="s">
+        <v>959</v>
+      </c>
+      <c r="U66" s="28" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="L62" s="20" t="s">
+      <c r="C67" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="O62" s="15" t="s">
+      <c r="E67" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="K67" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="S62" s="18" t="s">
+      <c r="L67" s="18" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+      <c r="M67" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="P67" s="15" t="s">
         <v>513</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="Q67" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="L63" s="20" t="s">
+      <c r="T67" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="O63" s="15" t="s">
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="P63" s="16" t="s">
+      <c r="C68" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="S63" s="18" t="s">
+      <c r="D68" s="5" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="K68" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="L68" s="18" t="s">
         <v>520</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="M68" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="P68" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="Q68" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="J64" s="10" t="s">
+      <c r="T68" s="18" t="s">
+        <v>961</v>
+      </c>
+      <c r="U68" s="28" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="C69" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="L64" s="20" t="s">
+      <c r="D69" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="O64" s="15" t="s">
+      <c r="E69" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="P64" s="16" t="s">
+      <c r="J69" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="S64" s="18" t="s">
+      <c r="K69" s="11" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="L69" s="18" t="s">
         <v>529</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="M69" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="O69" s="14" t="s">
         <v>530</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="E65" s="6" t="s">
+      <c r="P69" s="15" t="s">
         <v>531</v>
       </c>
-      <c r="J65" s="10" t="s">
+      <c r="Q69" s="16" t="s">
         <v>532</v>
       </c>
-      <c r="L65" s="20" t="s">
+      <c r="R69" s="17" t="s">
         <v>533</v>
       </c>
-      <c r="N65" s="14" t="s">
+      <c r="S69" s="18"/>
+      <c r="T69" s="18" t="s">
         <v>534</v>
       </c>
-      <c r="O65" s="15" t="s">
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="P65" s="16" t="s">
+      <c r="B70" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="S65" s="18" t="s">
+      <c r="C70" s="4" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="E70" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="F70" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="K70" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="L70" s="18" t="s">
         <v>541</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="M70" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="P70" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="Q70" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="L66" s="12" t="s">
+      <c r="T70" s="18" t="s">
+        <v>963</v>
+      </c>
+      <c r="U70" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="V70" s="28" t="s">
+        <v>965</v>
+      </c>
+      <c r="W70" t="s">
+        <v>966</v>
+      </c>
+      <c r="X70" t="s">
+        <v>967</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="O66" s="15" t="s">
+      <c r="B71" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="S66" s="18" t="s">
+      <c r="C71" s="4" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="E71" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="K71" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="K67" s="11" t="s">
+      <c r="L71" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="L67" s="20" t="s">
+      <c r="M71" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="P71" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="O67" s="15" t="s">
+      <c r="Q71" s="16" t="s">
         <v>551</v>
       </c>
-      <c r="P67" s="16" t="s">
+      <c r="T71" s="18" t="s">
+        <v>969</v>
+      </c>
+      <c r="U71" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="V71" s="28" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="S67" s="18" t="s">
+      <c r="B72" s="3" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="C72" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="D72" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="E72" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="J72" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="L72" t="s">
         <v>557</v>
       </c>
-      <c r="L68" s="20" t="s">
+      <c r="M72" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="P72" s="15" t="s">
         <v>558</v>
       </c>
-      <c r="O68" s="15" t="s">
+      <c r="Q72" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="P68" s="16" t="s">
+      <c r="T72" s="18" t="s">
+        <v>972</v>
+      </c>
+      <c r="U72" s="28" t="s">
+        <v>973</v>
+      </c>
+      <c r="V72" s="28" t="s">
+        <v>974</v>
+      </c>
+      <c r="W72" t="s">
+        <v>975</v>
+      </c>
+      <c r="X72" t="s">
+        <v>976</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>977</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="S68" s="18" t="s">
+      <c r="L73" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="M73" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="P73" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="Q73" s="16" t="s">
         <v>563</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="T73" s="18" t="s">
+        <v>979</v>
+      </c>
+      <c r="U73" s="28" t="s">
+        <v>980</v>
+      </c>
+      <c r="V73" s="28" t="s">
+        <v>981</v>
+      </c>
+      <c r="W73" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="C74" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="J69" s="10" t="s">
+      <c r="D74" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="E74" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="L69" s="12" t="s">
+      <c r="K74" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="N69" s="14" t="s">
+      <c r="L74" s="18" t="s">
         <v>569</v>
       </c>
-      <c r="O69" s="15" t="s">
+      <c r="M74" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="P74" s="15" t="s">
         <v>570</v>
       </c>
-      <c r="P69" s="16" t="s">
+      <c r="Q74" s="16" t="s">
         <v>571</v>
       </c>
-      <c r="Q69" s="17" t="s">
+      <c r="R74" s="17" t="s">
         <v>572</v>
       </c>
-      <c r="R69" s="18"/>
-      <c r="S69" s="18" t="s">
+      <c r="S74" s="18"/>
+      <c r="T74" s="18" t="s">
+        <v>983</v>
+      </c>
+      <c r="U74" s="28" t="s">
+        <v>984</v>
+      </c>
+      <c r="V74" s="28" t="s">
+        <v>985</v>
+      </c>
+      <c r="W74" t="s">
+        <v>986</v>
+      </c>
+      <c r="X74" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="C75" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="D75" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="E75" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="L75" t="s">
         <v>577</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="M75" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="P75" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="Q75" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="L70" s="12" t="s">
+      <c r="T75" s="18" t="s">
+        <v>988</v>
+      </c>
+      <c r="U75" s="28" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="O70" s="15" t="s">
+      <c r="B76" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="P70" s="16" t="s">
+      <c r="J76" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="S70" s="18" t="s">
+      <c r="K76" s="11" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+      <c r="L76" s="18" t="s">
         <v>584</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="M76" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="P76" s="15" t="s">
         <v>585</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="Q76" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="T76" s="18" t="s">
+        <v>990</v>
+      </c>
+      <c r="U76" s="28" t="s">
+        <v>991</v>
+      </c>
+      <c r="V76" s="28" t="s">
+        <v>992</v>
+      </c>
+      <c r="W76">
+        <v>4243135080</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="B77" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="L71" s="12" t="s">
+      <c r="E77" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="O71" s="15" t="s">
+      <c r="K77" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="P71" s="16" t="s">
+      <c r="L77" s="18" t="s">
         <v>591</v>
       </c>
-      <c r="S71" s="18" t="s">
+      <c r="M77" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="P77" s="15" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="Q77" s="16" t="s">
         <v>593</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="R77" s="17" t="s">
         <v>594</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="S77" s="18"/>
+      <c r="T77" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="U77" s="28" t="s">
+        <v>994</v>
+      </c>
+      <c r="V77" s="28" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="C78" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="J72" s="10" t="s">
+      <c r="E78" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="L72" s="12" t="s">
+      <c r="J78" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="O72" s="15" t="s">
+      <c r="K78" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="P72" s="16" t="s">
+      <c r="L78" s="18" t="s">
         <v>600</v>
       </c>
-      <c r="S72" s="18" t="s">
+      <c r="M78" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="P78" s="15" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="Q78" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="L73" s="12" t="s">
+      <c r="R78" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="O73" s="15" t="s">
+      <c r="S78" s="18"/>
+      <c r="T78" s="18" t="s">
+        <v>996</v>
+      </c>
+      <c r="U78" s="28" t="s">
+        <v>997</v>
+      </c>
+      <c r="V78" s="28" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="P73" s="16" t="s">
+      <c r="B79" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="S73" s="18" t="s">
+      <c r="K79" s="11" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="L79" s="18" t="s">
         <v>607</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="M79" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="P79" s="15" t="s">
         <v>608</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="Q79" s="16" t="s">
         <v>609</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="R79" s="17" t="s">
         <v>610</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="S79" s="18"/>
+      <c r="T79" s="18" t="s">
+        <v>999</v>
+      </c>
+      <c r="U79" s="28" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="L74" s="12" t="s">
+      <c r="B80" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="O74" s="15" t="s">
+      <c r="C80" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="P74" s="16" t="s">
+      <c r="D80" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="Q74" s="17" t="s">
+      <c r="E80" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="R74" s="18"/>
-      <c r="S74" s="18" t="s">
+      <c r="J80" s="10" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="K80" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="L80" s="18" t="s">
         <v>618</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="M80" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="O80" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="P80" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="L75" s="12" t="s">
+      <c r="Q80" s="16" t="s">
         <v>621</v>
       </c>
-      <c r="O75" s="15" t="s">
+      <c r="T80" s="18" t="s">
         <v>622</v>
       </c>
-      <c r="P75" s="16" t="s">
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="S75" s="18" t="s">
+      <c r="B81" s="3" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+      <c r="C81" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="D81" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="J76" s="10" t="s">
+      <c r="E81" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="J81" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="L76" s="12" t="s">
+      <c r="K81" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="O76" s="15" t="s">
+      <c r="L81" s="18" t="s">
         <v>630</v>
       </c>
-      <c r="P76" s="16" t="s">
+      <c r="M81" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="P81" s="15" t="s">
         <v>631</v>
       </c>
-      <c r="S76" s="18" t="s">
+      <c r="Q81" s="16" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+      <c r="R81" s="17" t="s">
         <v>633</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="S81" s="18"/>
+      <c r="T81" s="18" t="s">
         <v>634</v>
       </c>
-      <c r="E77" s="6" t="s">
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="C82" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="L77" s="12" t="s">
+      <c r="D82" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="O77" s="15" t="s">
+      <c r="F82" s="7" t="s">
         <v>638</v>
       </c>
-      <c r="P77" s="16" t="s">
+      <c r="J82" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="Q77" s="17" t="s">
+      <c r="K82" s="11" t="s">
         <v>640</v>
       </c>
-      <c r="R77" s="18"/>
-      <c r="S77" s="18" t="s">
+      <c r="L82" s="18" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="M82" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="O82" s="14" t="s">
         <v>642</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="P82" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="Q82" s="16" t="s">
         <v>644</v>
       </c>
-      <c r="J78" s="10" t="s">
+      <c r="T82" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="K78" s="11" t="s">
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="L78" s="12" t="s">
+      <c r="B83" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="O78" s="15" t="s">
+      <c r="C83" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="P78" s="16" t="s">
+      <c r="D83" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="Q78" s="17" t="s">
+      <c r="E83" s="6" t="s">
         <v>650</v>
       </c>
-      <c r="R78" s="18"/>
-      <c r="S78" s="18" t="s">
+      <c r="F83" s="7" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+      <c r="J83" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="K83" s="11" t="s">
         <v>653</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="L83" s="18" t="s">
         <v>654</v>
       </c>
-      <c r="L79" s="12" t="s">
+      <c r="M83" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="P83" s="15" t="s">
         <v>655</v>
       </c>
-      <c r="O79" s="15" t="s">
+      <c r="Q83" s="16" t="s">
         <v>656</v>
       </c>
-      <c r="P79" s="16" t="s">
+      <c r="T83" s="18" t="s">
+        <v>1001</v>
+      </c>
+      <c r="U83" s="28" t="s">
+        <v>1002</v>
+      </c>
+      <c r="V83" s="28" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="Q79" s="17" t="s">
+      <c r="C84" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="R79" s="18"/>
-      <c r="S79" s="18" t="s">
+      <c r="D84" s="5" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+      <c r="E84" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="F84" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="J84" s="10" t="s">
         <v>662</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="K84" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="L84" s="18" t="s">
         <v>664</v>
       </c>
-      <c r="J80" s="10" t="s">
+      <c r="M84" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="O84" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="R84" s="17" t="s">
         <v>666</v>
       </c>
-      <c r="L80" s="12" t="s">
+      <c r="S84" s="18"/>
+      <c r="T84" s="18" t="s">
+        <v>1004</v>
+      </c>
+      <c r="U84" s="28" t="s">
+        <v>1005</v>
+      </c>
+      <c r="V84" s="28" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="N80" s="14" t="s">
+      <c r="C85" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="O80" s="15" t="s">
+      <c r="D85" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="P80" s="16" t="s">
+      <c r="K85" s="11" t="s">
         <v>670</v>
       </c>
-      <c r="S80" s="18" t="s">
+      <c r="L85" s="18" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="M85" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="P85" s="15" t="s">
         <v>672</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="Q85" s="16" t="s">
         <v>673</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="R85" s="17" t="s">
         <v>674</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="S85" s="18"/>
+      <c r="T85" s="18" t="s">
         <v>675</v>
       </c>
-      <c r="E81" s="6" t="s">
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" s="21" t="s">
         <v>676</v>
       </c>
-      <c r="J81" s="10" t="s">
+      <c r="M86" s="22"/>
+      <c r="T86" s="22"/>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="C87" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="L81" s="12" t="s">
+      <c r="D87" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="O81" s="15" t="s">
+      <c r="E87" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="P81" s="16" t="s">
+      <c r="F87" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="Q81" s="17" t="s">
+      <c r="J87" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="R81" s="18"/>
-      <c r="S81" s="18" t="s">
+      <c r="K87" s="11" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+      <c r="L87" s="18" t="s">
         <v>684</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="M87" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="O87" s="14" t="s">
         <v>685</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="Q87" s="16" t="s">
         <v>686</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="R87" s="17" t="s">
         <v>687</v>
       </c>
-      <c r="J82" s="10" t="s">
+      <c r="S87" s="18"/>
+      <c r="T87" s="18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="U87" s="28" t="s">
+        <v>1008</v>
+      </c>
+      <c r="V87" s="28" t="s">
+        <v>1009</v>
+      </c>
+      <c r="W87">
+        <v>9004417</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="B88" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="L82" s="12" t="s">
+      <c r="C88" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="N82" s="14" t="s">
+      <c r="D88" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="O82" s="15" t="s">
+      <c r="E88" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="P82" s="16" t="s">
+      <c r="F88" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="S82" s="18" t="s">
+      <c r="L88" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+      <c r="M88" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="R88" s="17" t="s">
         <v>695</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="S88" s="18"/>
+      <c r="T88" s="18" t="s">
+        <v>1010</v>
+      </c>
+      <c r="U88" s="28" t="s">
+        <v>1011</v>
+      </c>
+      <c r="V88" s="28" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="B89" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="L89" t="s">
         <v>699</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="M89" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="R89" s="17" t="s">
         <v>700</v>
       </c>
-      <c r="J83" s="10" t="s">
+      <c r="S89" s="18"/>
+      <c r="T89" s="18" t="s">
+        <v>1013</v>
+      </c>
+      <c r="U89" s="28" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="C90" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="L83" s="12" t="s">
+      <c r="D90" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="O83" s="15" t="s">
+      <c r="E90" s="6" t="s">
         <v>704</v>
       </c>
-      <c r="P83" s="16" t="s">
+      <c r="K90" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="S83" s="18" t="s">
+      <c r="L90" s="18" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+      <c r="M90" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q90" s="16" t="s">
         <v>707</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="R90" s="17" t="s">
         <v>708</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="S90" s="18"/>
+      <c r="T90" s="18" t="s">
+        <v>1015</v>
+      </c>
+      <c r="U90" s="28" t="s">
+        <v>1016</v>
+      </c>
+      <c r="V90" s="28" t="s">
+        <v>1017</v>
+      </c>
+      <c r="W90">
+        <v>5841129000</v>
+      </c>
+      <c r="X90">
+        <v>5275129000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="F91" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="K91" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="J84" s="10" t="s">
+      <c r="L91" s="18" t="s">
         <v>712</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="M91" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q91" s="16" t="s">
         <v>713</v>
       </c>
-      <c r="L84" s="12" t="s">
+      <c r="R91" s="17" t="s">
         <v>714</v>
       </c>
-      <c r="N84" s="14" t="s">
+      <c r="S91" s="18"/>
+      <c r="T91" s="18" t="s">
+        <v>1018</v>
+      </c>
+      <c r="U91" s="28" t="s">
+        <v>1019</v>
+      </c>
+      <c r="V91" s="28" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="Q84" s="17" t="s">
+      <c r="L92" t="s">
         <v>716</v>
       </c>
-      <c r="R84" s="18"/>
-      <c r="S84" s="18" t="s">
+      <c r="M92" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="Q92" s="16" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+      <c r="R92" s="17" t="s">
         <v>718</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="S92" s="18"/>
+      <c r="T92" s="18" t="s">
         <v>719</v>
       </c>
-      <c r="D85" s="5" t="s">
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="D93" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="L85" s="12" t="s">
+      <c r="F93" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="O85" s="15" t="s">
+      <c r="J93" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="P85" s="16" t="s">
+      <c r="K93" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="Q85" s="17" t="s">
+      <c r="L93" s="18" t="s">
         <v>725</v>
       </c>
-      <c r="R85" s="18"/>
-      <c r="S85" s="18" t="s">
+      <c r="M93" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="Q93" s="16" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A86" s="21" t="s">
+      <c r="R93" s="17" t="s">
         <v>727</v>
       </c>
-      <c r="L86" s="22"/>
-      <c r="S86" s="22"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+      <c r="S93" s="18"/>
+      <c r="T93" s="18" t="s">
         <v>728</v>
       </c>
-      <c r="C87" s="4" t="s">
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="B94" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="E87" s="6" t="s">
+      <c r="L94" t="s">
         <v>731</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="M94" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="Q94" s="16" t="s">
         <v>732</v>
       </c>
-      <c r="J87" s="10" t="s">
+      <c r="T94" s="18" t="s">
+        <v>1021</v>
+      </c>
+      <c r="U94" s="28" t="s">
+        <v>1022</v>
+      </c>
+      <c r="V94" s="28" t="s">
+        <v>1023</v>
+      </c>
+      <c r="W94">
+        <v>7701463277</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="B95" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="L87" s="12" t="s">
+      <c r="K95" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="N87" s="14" t="s">
+      <c r="L95" s="18" t="s">
         <v>736</v>
       </c>
-      <c r="P87" s="16" t="s">
+      <c r="M95" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="Q95" s="16" t="s">
         <v>737</v>
       </c>
-      <c r="Q87" s="17" t="s">
+      <c r="R95" s="17" t="s">
         <v>738</v>
       </c>
-      <c r="R87" s="18"/>
-      <c r="S87" s="18" t="s">
+      <c r="S95" s="18"/>
+      <c r="T95" s="18" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B96" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="F96" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="K96" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="E88" s="6" t="s">
+      <c r="L96" s="18" t="s">
         <v>744</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="M96" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="R96" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="L88" s="12" t="s">
+      <c r="S96" s="18"/>
+      <c r="T96" s="18" t="s">
+        <v>1024</v>
+      </c>
+      <c r="U96" s="28" t="s">
+        <v>1025</v>
+      </c>
+      <c r="V96" s="28" t="s">
+        <v>1026</v>
+      </c>
+      <c r="W96">
+        <v>51900802</v>
+      </c>
+      <c r="X96">
+        <v>7599325</v>
+      </c>
+      <c r="Y96">
+        <v>7750119</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="Q88" s="17" t="s">
+      <c r="B97" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="R88" s="18"/>
-      <c r="S88" s="18" t="s">
+      <c r="L97" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="M97" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="R97" s="17" t="s">
         <v>749</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="S97" s="18"/>
+      <c r="T97" s="18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="U97" s="28" t="s">
+        <v>1028</v>
+      </c>
+      <c r="V97" s="28" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="K98" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="L89" s="12" t="s">
+      <c r="L98" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="Q89" s="17" t="s">
+      <c r="M98" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="R98" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="R89" s="18"/>
-      <c r="S89" s="18" t="s">
+      <c r="S98" s="18"/>
+      <c r="T98" s="18" t="s">
+        <v>1030</v>
+      </c>
+      <c r="U98" s="28" t="s">
+        <v>1031</v>
+      </c>
+      <c r="V98" s="28" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="B99" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="K99" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="L99" s="18" t="s">
         <v>757</v>
       </c>
-      <c r="E90" s="6" t="s">
+      <c r="M99" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="O99" s="14" t="s">
         <v>758</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="T99" s="18" t="s">
         <v>759</v>
       </c>
-      <c r="L90" s="12" t="s">
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="P90" s="16" t="s">
+      <c r="K100" s="11" t="s">
         <v>761</v>
       </c>
-      <c r="Q90" s="17" t="s">
+      <c r="L100" s="18" t="s">
         <v>762</v>
       </c>
-      <c r="R90" s="18"/>
-      <c r="S90" s="18" t="s">
+      <c r="M100" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="P100" s="15" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+      <c r="T100" s="18" t="s">
+        <v>1033</v>
+      </c>
+      <c r="U100" s="28" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="B101" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K101" s="11" t="s">
         <v>766</v>
       </c>
-      <c r="L91" s="12" t="s">
+      <c r="L101" s="18" t="s">
         <v>767</v>
       </c>
-      <c r="P91" s="16" t="s">
+      <c r="M101" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="R101" s="17" t="s">
         <v>768</v>
       </c>
-      <c r="Q91" s="17" t="s">
+      <c r="S101" s="18"/>
+      <c r="T101" s="18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="U101" s="28" t="s">
+        <v>1036</v>
+      </c>
+      <c r="V101" s="28" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="R91" s="18"/>
-      <c r="S91" s="18" t="s">
+      <c r="B102" s="3" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="T102" s="18" t="s">
+        <v>1038</v>
+      </c>
+      <c r="U102" s="28" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="L92" s="12" t="s">
+      <c r="D103" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="P92" s="16" t="s">
+      <c r="E103" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="Q92" s="17" t="s">
+      <c r="R103" s="17" t="s">
         <v>774</v>
       </c>
-      <c r="R92" s="18"/>
-      <c r="S92" s="18" t="s">
+      <c r="S103" s="18"/>
+      <c r="T103" s="18" t="s">
+        <v>1040</v>
+      </c>
+      <c r="U103" s="28" t="s">
+        <v>1041</v>
+      </c>
+      <c r="V103" s="28" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A104" s="21" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+      <c r="M104" s="22"/>
+      <c r="T104" s="21" t="s">
+        <v>907</v>
+      </c>
+      <c r="U104" s="28" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="C105" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="D105" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="K105" s="11" t="s">
         <v>778</v>
       </c>
-      <c r="J93" s="10" t="s">
+      <c r="L105" s="18" t="s">
         <v>779</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="M105" s="20" t="s">
+        <v>779</v>
+      </c>
+      <c r="O105" s="14" t="s">
         <v>780</v>
       </c>
-      <c r="L93" s="12" t="s">
+      <c r="T105" s="18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="U105" s="28" t="s">
+        <v>1044</v>
+      </c>
+      <c r="V105" s="28" t="s">
+        <v>1045</v>
+      </c>
+      <c r="W105">
+        <v>52015297</v>
+      </c>
+      <c r="X105">
+        <v>568002</v>
+      </c>
+      <c r="Y105">
+        <v>95515120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="P93" s="16" t="s">
+      <c r="K106" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="Q93" s="17" t="s">
+      <c r="L106" s="18" t="s">
         <v>783</v>
       </c>
-      <c r="R93" s="18"/>
-      <c r="S93" s="18" t="s">
+      <c r="M106" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="T106" s="18" t="s">
+        <v>1046</v>
+      </c>
+      <c r="U106" s="28" t="s">
+        <v>1047</v>
+      </c>
+      <c r="V106" s="28" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
+      <c r="F107" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="L107" t="s">
         <v>785</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="M107" s="21"/>
+      <c r="T107" s="18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="U107" s="28" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="L94" s="12" t="s">
+      <c r="I108" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="P94" s="16" t="s">
+      <c r="K108" s="11" t="s">
         <v>788</v>
       </c>
-      <c r="S94" s="18" t="s">
+      <c r="L108" s="18" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+      <c r="M108" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="O108" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="T108" s="18" t="s">
         <v>791</v>
       </c>
-      <c r="K95" s="11" t="s">
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A109" s="21" t="s">
         <v>792</v>
       </c>
-      <c r="L95" s="12" t="s">
-        <v>793</v>
-      </c>
-      <c r="P95" s="16" t="s">
+      <c r="T109" s="21" t="s">
+        <v>1051</v>
+      </c>
+      <c r="U109" s="28" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A110" s="21" t="s">
         <v>794</v>
       </c>
-      <c r="Q95" s="17" t="s">
+      <c r="T110" s="21" t="s">
         <v>795</v>
       </c>
-      <c r="R95" s="18"/>
-      <c r="S95" s="18" t="s">
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A111" s="21" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="B96" s="3" t="s">
+      <c r="T111" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="U111" s="28" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A112" s="21" t="s">
         <v>798</v>
       </c>
-      <c r="F96" s="7" t="s">
+      <c r="T112" s="21" t="s">
         <v>799</v>
       </c>
-      <c r="K96" s="11" t="s">
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A113" s="21" t="s">
         <v>800</v>
       </c>
-      <c r="L96" s="12" t="s">
-        <v>801</v>
-      </c>
-      <c r="Q96" s="17" t="s">
+      <c r="T113" s="21" t="s">
+        <v>1055</v>
+      </c>
+      <c r="U113" s="28" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="R96" s="18"/>
-      <c r="S96" s="18" t="s">
+      <c r="B114" s="3" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+      <c r="T114" s="18" t="s">
+        <v>1057</v>
+      </c>
+      <c r="U114" s="28" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="K115" s="11" t="s">
         <v>805</v>
       </c>
-      <c r="L97" s="12" t="s">
+      <c r="L115" s="18" t="s">
         <v>806</v>
       </c>
-      <c r="Q97" s="17" t="s">
+      <c r="M115" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="T115" s="18" t="s">
         <v>807</v>
       </c>
-      <c r="R97" s="18"/>
-      <c r="S97" s="18" t="s">
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
+      <c r="C116" s="4" t="s">
         <v>809</v>
       </c>
-      <c r="K98" s="11" t="s">
+      <c r="H116" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="L98" s="12" t="s">
+      <c r="R116" s="17" t="s">
         <v>811</v>
       </c>
-      <c r="Q98" s="17" t="s">
+      <c r="S116" s="18"/>
+      <c r="T116" s="18" t="s">
+        <v>1059</v>
+      </c>
+      <c r="U116" s="28" t="s">
+        <v>1060</v>
+      </c>
+      <c r="V116" s="28" t="s">
+        <v>1061</v>
+      </c>
+      <c r="W116" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="R98" s="18"/>
-      <c r="S98" s="18" t="s">
+      <c r="B117" s="3" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+      <c r="C117" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="L117" t="s">
         <v>815</v>
       </c>
-      <c r="K99" s="11" t="s">
+      <c r="M117" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="R117" s="17" t="s">
         <v>816</v>
       </c>
-      <c r="L99" s="12" t="s">
+      <c r="S117" s="18"/>
+      <c r="T117" s="18" t="s">
+        <v>1063</v>
+      </c>
+      <c r="U117" s="28" t="s">
+        <v>1064</v>
+      </c>
+      <c r="V117" s="28" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="N99" s="14" t="s">
+      <c r="S118" s="23" t="s">
+        <v>847</v>
+      </c>
+      <c r="T118" s="18" t="s">
         <v>818</v>
       </c>
-      <c r="S99" s="18" t="s">
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="S119" s="23" t="s">
+        <v>848</v>
+      </c>
+      <c r="T119" s="18" t="s">
+        <v>1066</v>
+      </c>
+      <c r="U119" s="28" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="K100" s="11" t="s">
+      <c r="B120" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="L100" s="12" t="s">
+      <c r="L120" t="s">
         <v>822</v>
       </c>
-      <c r="O100" s="15" t="s">
+      <c r="M120" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q120" s="16" t="s">
         <v>823</v>
       </c>
-      <c r="S100" s="18" t="s">
+      <c r="T120" s="18" t="s">
+        <v>1068</v>
+      </c>
+      <c r="U120" s="28" t="s">
+        <v>1069</v>
+      </c>
+      <c r="V120" s="28" t="s">
+        <v>1070</v>
+      </c>
+      <c r="W120" t="s">
+        <v>1071</v>
+      </c>
+      <c r="X120" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="K121" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="L121" s="18" t="s">
         <v>826</v>
       </c>
-      <c r="K101" s="11" t="s">
+      <c r="M121" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="T121" s="18" t="s">
+        <v>1073</v>
+      </c>
+      <c r="U121" s="28" t="s">
+        <v>1074</v>
+      </c>
+      <c r="V121" s="28" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="L101" s="12" t="s">
+      <c r="B122" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="Q101" s="17" t="s">
+      <c r="T122" s="18" t="s">
+        <v>1076</v>
+      </c>
+      <c r="U122" s="28" t="s">
+        <v>1077</v>
+      </c>
+      <c r="V122" s="28" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A123" s="21" t="s">
         <v>829</v>
       </c>
-      <c r="R101" s="18"/>
-      <c r="S101" s="18" t="s">
+      <c r="T123" s="22"/>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A124" s="21" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+      <c r="T124" s="21" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="R125" s="23">
+        <v>94036400</v>
+      </c>
+      <c r="T125" s="18" t="s">
+        <v>1079</v>
+      </c>
+      <c r="U125" s="28" t="s">
+        <v>1080</v>
+      </c>
+      <c r="V125" s="28" t="s">
+        <v>1081</v>
+      </c>
+      <c r="W125" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X125" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>1080</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AA125" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AB125" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="S102" s="18" t="s">
+      <c r="B126" s="23" t="s">
+        <v>850</v>
+      </c>
+      <c r="T126" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="U126" s="28" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V126" s="28" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+      <c r="R127" s="17" t="s">
         <v>834</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="S127" s="18"/>
+      <c r="T127" s="18" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U127" s="28" t="s">
+        <v>1089</v>
+      </c>
+      <c r="V127" s="28" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W127" t="s">
+        <v>1091</v>
+      </c>
+      <c r="X127" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="E103" s="6" t="s">
+      <c r="R128" s="17" t="s">
         <v>836</v>
       </c>
-      <c r="Q103" s="17" t="s">
-        <v>837</v>
-      </c>
-      <c r="R103" s="18"/>
-      <c r="S103" s="18" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A104" s="21" t="s">
-        <v>839</v>
-      </c>
-      <c r="L104" s="22"/>
-      <c r="S104" s="21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="K105" s="11" t="s">
-        <v>842</v>
-      </c>
-      <c r="L105" s="20" t="s">
-        <v>843</v>
-      </c>
-      <c r="N105" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="S105" s="18" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="K106" s="11" t="s">
-        <v>847</v>
-      </c>
-      <c r="L106" s="12" t="s">
-        <v>848</v>
-      </c>
-      <c r="S106" s="18" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="L107" s="21" t="s">
-        <v>851</v>
-      </c>
-      <c r="S107" s="18" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="I108" s="9" t="s">
-        <v>854</v>
-      </c>
-      <c r="K108" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="L108" s="12" t="s">
-        <v>856</v>
-      </c>
-      <c r="N108" s="14" t="s">
-        <v>857</v>
-      </c>
-      <c r="S108" s="18" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A109" s="21" t="s">
-        <v>859</v>
-      </c>
-      <c r="S109" s="21" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A110" s="21" t="s">
-        <v>861</v>
-      </c>
-      <c r="S110" s="21" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A111" s="21" t="s">
-        <v>863</v>
-      </c>
-      <c r="S111" s="21" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A112" s="21" t="s">
-        <v>865</v>
-      </c>
-      <c r="S112" s="21" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A113" s="21" t="s">
-        <v>867</v>
-      </c>
-      <c r="S113" s="21" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="S114" s="18" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="K115" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="L115" s="12" t="s">
-        <v>874</v>
-      </c>
-      <c r="S115" s="18" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>877</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="Q116" s="17" t="s">
-        <v>879</v>
-      </c>
-      <c r="R116" s="18"/>
-      <c r="S116" s="18" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>883</v>
-      </c>
-      <c r="L117" s="12" t="s">
-        <v>884</v>
-      </c>
-      <c r="Q117" s="17" t="s">
-        <v>885</v>
-      </c>
-      <c r="R117" s="18"/>
-      <c r="S117" s="18" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="R118" s="23" t="s">
-        <v>925</v>
-      </c>
-      <c r="S118" s="18" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="R119" s="23" t="s">
-        <v>926</v>
-      </c>
-      <c r="S119" s="18" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="L120" s="12" t="s">
-        <v>893</v>
-      </c>
-      <c r="P120" s="16" t="s">
-        <v>894</v>
-      </c>
-      <c r="S120" s="18" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="K121" s="11" t="s">
-        <v>897</v>
-      </c>
-      <c r="L121" s="12" t="s">
-        <v>898</v>
-      </c>
-      <c r="S121" s="18" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="S122" s="18" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A123" s="21" t="s">
-        <v>903</v>
-      </c>
-      <c r="S123" s="22"/>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A124" s="21" t="s">
-        <v>904</v>
-      </c>
-      <c r="S124" s="21" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="Q125" s="23">
-        <v>94036400</v>
-      </c>
-      <c r="S125" s="18" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="B126" s="23" t="s">
-        <v>928</v>
-      </c>
-      <c r="S126" s="18" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="Q127" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="R127" s="18"/>
-      <c r="S127" s="18" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="Q128" s="17" t="s">
-        <v>913</v>
-      </c>
-      <c r="R128" s="18"/>
-      <c r="S128" s="18" t="s">
-        <v>914</v>
+      <c r="S128" s="18"/>
+      <c r="T128" s="18" t="s">
+        <v>1093</v>
+      </c>
+      <c r="U128" s="28" t="s">
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S128" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T128" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6477,10 +7946,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="24" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>916</v>
+        <v>838</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>929</v>
+        <v>851</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -6496,7 +7965,7 @@
         <v>13278</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -6504,7 +7973,7 @@
         <v>13284</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6512,7 +7981,7 @@
         <v>45387</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -6520,12 +7989,12 @@
         <v>45396</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B7" s="25">
         <v>2952956</v>
@@ -6545,10 +8014,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
-        <v>839</v>
+        <v>775</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -6556,7 +8025,7 @@
         <v>63999</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>860</v>
+        <v>793</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -6564,7 +8033,7 @@
         <v>251070</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>862</v>
+        <v>795</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -6572,7 +8041,7 @@
         <v>401071</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>864</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -6588,12 +8057,12 @@
         <v>401073</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>868</v>
+        <v>801</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="26" t="s">
-        <v>903</v>
+        <v>829</v>
       </c>
       <c r="B16" s="26"/>
     </row>
@@ -6602,7 +8071,7 @@
         <v>251088</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>862</v>
+        <v>795</v>
       </c>
     </row>
   </sheetData>

--- a/src/resources/data/catalogInfo/excels/Drum_katalog_full.xlsx
+++ b/src/resources/data/catalogInfo/excels/Drum_katalog_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\URETIM9\Desktop\Projects\API_SCRAPE\src\resources\data\catalogInfo\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26B2EF8-A679-4404-8666-5D6B6CD506C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581D51E9-C8C2-41E2-9B98-B481E6AB5235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2220" windowWidth="20532" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="987">
   <si>
     <t>BREMBO</t>
   </si>
@@ -68,9 +68,6 @@
     <t>RAION stok kodu</t>
   </si>
   <si>
-    <t>24163</t>
-  </si>
-  <si>
     <t>14.3260.10</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>6014235101</t>
   </si>
   <si>
-    <t>24165</t>
-  </si>
-  <si>
     <t>14.5603.10</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
     <t>6014235001</t>
   </si>
   <si>
-    <t>13275</t>
-  </si>
-  <si>
     <t>07050077</t>
   </si>
   <si>
@@ -119,9 +110,6 @@
     <t>043860</t>
   </si>
   <si>
-    <t>13277</t>
-  </si>
-  <si>
     <t>14.3166.10</t>
   </si>
   <si>
@@ -146,9 +134,6 @@
     <t>6046462</t>
   </si>
   <si>
-    <t>13278</t>
-  </si>
-  <si>
     <t>07050079</t>
   </si>
   <si>
@@ -158,9 +143,6 @@
     <t>HST1126AB</t>
   </si>
   <si>
-    <t>13279</t>
-  </si>
-  <si>
     <t>14.6794.10</t>
   </si>
   <si>
@@ -176,9 +158,6 @@
     <t>BSG 30-225-023</t>
   </si>
   <si>
-    <t>13280</t>
-  </si>
-  <si>
     <t>07050081</t>
   </si>
   <si>
@@ -188,9 +167,6 @@
     <t>6049432</t>
   </si>
   <si>
-    <t>13281</t>
-  </si>
-  <si>
     <t>14.7099.10</t>
   </si>
   <si>
@@ -215,9 +191,6 @@
     <t>BSG 30-225-002</t>
   </si>
   <si>
-    <t>13282</t>
-  </si>
-  <si>
     <t>14.7098.10</t>
   </si>
   <si>
@@ -242,9 +215,6 @@
     <t>BSG 30-225-001</t>
   </si>
   <si>
-    <t>13283</t>
-  </si>
-  <si>
     <t>14.7008.10, 14.7247.10</t>
   </si>
   <si>
@@ -266,9 +236,6 @@
     <t>BSG 30-225-024</t>
   </si>
   <si>
-    <t>13284</t>
-  </si>
-  <si>
     <t>07050083</t>
   </si>
   <si>
@@ -278,9 +245,6 @@
     <t>90PY1126</t>
   </si>
   <si>
-    <t>13285</t>
-  </si>
-  <si>
     <t>14.A692.10</t>
   </si>
   <si>
@@ -308,9 +272,6 @@
     <t>94024600</t>
   </si>
   <si>
-    <t>13286</t>
-  </si>
-  <si>
     <t>14.A693.10</t>
   </si>
   <si>
@@ -332,9 +293,6 @@
     <t>94024800</t>
   </si>
   <si>
-    <t>13290</t>
-  </si>
-  <si>
     <t>14.A691.10</t>
   </si>
   <si>
@@ -356,9 +314,6 @@
     <t>94024400</t>
   </si>
   <si>
-    <t>13289</t>
-  </si>
-  <si>
     <t>DB4338B</t>
   </si>
   <si>
@@ -372,9 +327,6 @@
   </si>
   <si>
     <t>94022500</t>
-  </si>
-  <si>
-    <t>36020</t>
   </si>
   <si>
     <t>14.3256.10</t>
@@ -417,9 +369,6 @@
     <t>94006600</t>
   </si>
   <si>
-    <t>25181</t>
-  </si>
-  <si>
     <t>DB4313</t>
   </si>
   <si>
@@ -444,9 +393,6 @@
     <t>MB193595</t>
   </si>
   <si>
-    <t>18160</t>
-  </si>
-  <si>
     <t>DB4449</t>
   </si>
   <si>
@@ -468,9 +414,6 @@
     <t>BSG 40-225-007</t>
   </si>
   <si>
-    <t>16183</t>
-  </si>
-  <si>
     <t>DB4377</t>
   </si>
   <si>
@@ -489,9 +432,6 @@
     <t>BSG 40-225-006</t>
   </si>
   <si>
-    <t>33149</t>
-  </si>
-  <si>
     <t>14.7076.10</t>
   </si>
   <si>
@@ -522,9 +462,6 @@
     <t>94014600</t>
   </si>
   <si>
-    <t>40217</t>
-  </si>
-  <si>
     <t>14.4733.10</t>
   </si>
   <si>
@@ -546,9 +483,6 @@
     <t>BSG 41-225-004</t>
   </si>
   <si>
-    <t>28324</t>
-  </si>
-  <si>
     <t>14.3283.10</t>
   </si>
   <si>
@@ -582,9 +516,6 @@
     <t>424724</t>
   </si>
   <si>
-    <t>36349</t>
-  </si>
-  <si>
     <t>TFD-00611</t>
   </si>
   <si>
@@ -594,9 +525,6 @@
     <t>113501615J</t>
   </si>
   <si>
-    <t>40371</t>
-  </si>
-  <si>
     <t>14.D629.10</t>
   </si>
   <si>
@@ -618,9 +546,6 @@
     <t>8973605050</t>
   </si>
   <si>
-    <t>40372</t>
-  </si>
-  <si>
     <t>14.D630.10</t>
   </si>
   <si>
@@ -642,9 +567,6 @@
     <t>BSG 41-225-002</t>
   </si>
   <si>
-    <t>27381</t>
-  </si>
-  <si>
     <t>14.7715.10</t>
   </si>
   <si>
@@ -672,9 +594,6 @@
     <t>94022600</t>
   </si>
   <si>
-    <t>27382</t>
-  </si>
-  <si>
     <t>14.4719.10</t>
   </si>
   <si>
@@ -705,9 +624,6 @@
     <t>BSG 65-225-002</t>
   </si>
   <si>
-    <t>27383</t>
-  </si>
-  <si>
     <t>14.4718.10</t>
   </si>
   <si>
@@ -735,9 +651,6 @@
     <t>BSG 65-225-004</t>
   </si>
   <si>
-    <t>27384</t>
-  </si>
-  <si>
     <t>14.4978.10</t>
   </si>
   <si>
@@ -768,27 +681,18 @@
     <t>94009900</t>
   </si>
   <si>
-    <t>45387</t>
-  </si>
-  <si>
     <t>TFD-00682</t>
   </si>
   <si>
     <t>3757089, 921750</t>
   </si>
   <si>
-    <t>45396</t>
-  </si>
-  <si>
     <t>TFD-00683</t>
   </si>
   <si>
     <t>28288, 18019</t>
   </si>
   <si>
-    <t>25412</t>
-  </si>
-  <si>
     <t>14.7096.10</t>
   </si>
   <si>
@@ -828,9 +732,6 @@
     <t>2952956</t>
   </si>
   <si>
-    <t>28431</t>
-  </si>
-  <si>
     <t>AD5006</t>
   </si>
   <si>
@@ -840,9 +741,6 @@
     <t>TFD-00523</t>
   </si>
   <si>
-    <t>51435</t>
-  </si>
-  <si>
     <t>14.A680.10</t>
   </si>
   <si>
@@ -855,9 +753,6 @@
     <t>4243187602000</t>
   </si>
   <si>
-    <t>27447</t>
-  </si>
-  <si>
     <t>14.A694.10</t>
   </si>
   <si>
@@ -882,9 +777,6 @@
     <t>94031500</t>
   </si>
   <si>
-    <t>27448</t>
-  </si>
-  <si>
     <t>14.A702.10</t>
   </si>
   <si>
@@ -915,18 +807,12 @@
     <t>94024100</t>
   </si>
   <si>
-    <t>18455</t>
-  </si>
-  <si>
     <t>07050025</t>
   </si>
   <si>
     <t>TFD-00397</t>
   </si>
   <si>
-    <t>26463</t>
-  </si>
-  <si>
     <t>14.6774.10</t>
   </si>
   <si>
@@ -945,15 +831,9 @@
     <t>4320631G11</t>
   </si>
   <si>
-    <t>45473</t>
-  </si>
-  <si>
     <t>TFD-00688</t>
   </si>
   <si>
-    <t>59480</t>
-  </si>
-  <si>
     <t>AD5048</t>
   </si>
   <si>
@@ -966,9 +846,6 @@
     <t>57RS305352</t>
   </si>
   <si>
-    <t>27504</t>
-  </si>
-  <si>
     <t>14.9390.10</t>
   </si>
   <si>
@@ -999,9 +876,6 @@
     <t>568060</t>
   </si>
   <si>
-    <t>16508</t>
-  </si>
-  <si>
     <t>BD-5131</t>
   </si>
   <si>
@@ -1023,9 +897,6 @@
     <t>BSG 40-225-001</t>
   </si>
   <si>
-    <t>25509</t>
-  </si>
-  <si>
     <t>DB4423</t>
   </si>
   <si>
@@ -1053,9 +924,6 @@
     <t>94035300</t>
   </si>
   <si>
-    <t>16518</t>
-  </si>
-  <si>
     <t>BF520</t>
   </si>
   <si>
@@ -1080,9 +948,6 @@
     <t>5276144000</t>
   </si>
   <si>
-    <t>59519</t>
-  </si>
-  <si>
     <t>AD5059</t>
   </si>
   <si>
@@ -1095,9 +960,6 @@
     <t>5M66346</t>
   </si>
   <si>
-    <t>36532</t>
-  </si>
-  <si>
     <t>14.9384.20</t>
   </si>
   <si>
@@ -1134,9 +996,6 @@
     <t>94023800</t>
   </si>
   <si>
-    <t>13544</t>
-  </si>
-  <si>
     <t>BG4064</t>
   </si>
   <si>
@@ -1158,9 +1017,6 @@
     <t>94045600</t>
   </si>
   <si>
-    <t>16561</t>
-  </si>
-  <si>
     <t>DB4422</t>
   </si>
   <si>
@@ -1185,9 +1041,6 @@
     <t>94035900</t>
   </si>
   <si>
-    <t>34565</t>
-  </si>
-  <si>
     <t>14.5815.10</t>
   </si>
   <si>
@@ -1212,9 +1065,6 @@
     <t>BSG 85-225-001</t>
   </si>
   <si>
-    <t>40569</t>
-  </si>
-  <si>
     <t>DB4452</t>
   </si>
   <si>
@@ -1239,9 +1089,6 @@
     <t>94039400</t>
   </si>
   <si>
-    <t>36571</t>
-  </si>
-  <si>
     <t>14.9384.10</t>
   </si>
   <si>
@@ -1269,9 +1116,6 @@
     <t>6X0609617A</t>
   </si>
   <si>
-    <t>30579</t>
-  </si>
-  <si>
     <t>14.E312.60</t>
   </si>
   <si>
@@ -1290,9 +1134,6 @@
     <t>BSG 75-225-004</t>
   </si>
   <si>
-    <t>33591</t>
-  </si>
-  <si>
     <t>14.A855.10</t>
   </si>
   <si>
@@ -1338,9 +1179,6 @@
     <t>94047400</t>
   </si>
   <si>
-    <t>28593</t>
-  </si>
-  <si>
     <t>14.7714.10</t>
   </si>
   <si>
@@ -1353,9 +1191,6 @@
     <t>07040390</t>
   </si>
   <si>
-    <t>33740</t>
-  </si>
-  <si>
     <t>14.7127.20</t>
   </si>
   <si>
@@ -1386,9 +1221,6 @@
     <t>94014000</t>
   </si>
   <si>
-    <t>26747</t>
-  </si>
-  <si>
     <t>AD5049</t>
   </si>
   <si>
@@ -1407,9 +1239,6 @@
     <t>43206EB360</t>
   </si>
   <si>
-    <t>15701</t>
-  </si>
-  <si>
     <t>DB4020</t>
   </si>
   <si>
@@ -1431,9 +1260,6 @@
     <t>BSG 35-225-002</t>
   </si>
   <si>
-    <t>15702</t>
-  </si>
-  <si>
     <t>FDR329805</t>
   </si>
   <si>
@@ -1455,9 +1281,6 @@
     <t>42610S5A000</t>
   </si>
   <si>
-    <t>16703</t>
-  </si>
-  <si>
     <t>AD5055</t>
   </si>
   <si>
@@ -1470,9 +1293,6 @@
     <t>583294A200</t>
   </si>
   <si>
-    <t>16704</t>
-  </si>
-  <si>
     <t>AD5047</t>
   </si>
   <si>
@@ -1488,9 +1308,6 @@
     <t>5276147010</t>
   </si>
   <si>
-    <t>16705</t>
-  </si>
-  <si>
     <t>DB4267</t>
   </si>
   <si>
@@ -1518,9 +1335,6 @@
     <t>5841122100</t>
   </si>
   <si>
-    <t>16706</t>
-  </si>
-  <si>
     <t>DB4283</t>
   </si>
   <si>
@@ -1542,9 +1356,6 @@
     <t>BSG 40-225-008</t>
   </si>
   <si>
-    <t>16707</t>
-  </si>
-  <si>
     <t>14.C013.10</t>
   </si>
   <si>
@@ -1566,9 +1377,6 @@
     <t>RAI-KD02020</t>
   </si>
   <si>
-    <t>16708</t>
-  </si>
-  <si>
     <t>DB4416</t>
   </si>
   <si>
@@ -1587,9 +1395,6 @@
     <t>5841125201</t>
   </si>
   <si>
-    <t>16709</t>
-  </si>
-  <si>
     <t>DB4430</t>
   </si>
   <si>
@@ -1608,9 +1413,6 @@
     <t>BSG 40-225-011</t>
   </si>
   <si>
-    <t>16710</t>
-  </si>
-  <si>
     <t>DB4401</t>
   </si>
   <si>
@@ -1644,9 +1446,6 @@
     <t>584111C300</t>
   </si>
   <si>
-    <t>18711</t>
-  </si>
-  <si>
     <t>14.9394.10</t>
   </si>
   <si>
@@ -1671,9 +1470,6 @@
     <t>BSG 55-225-003</t>
   </si>
   <si>
-    <t>22712</t>
-  </si>
-  <si>
     <t>14.A700.10</t>
   </si>
   <si>
@@ -1695,9 +1491,6 @@
     <t>BSG 55-225-001</t>
   </si>
   <si>
-    <t>22713</t>
-  </si>
-  <si>
     <t>14.D631.10</t>
   </si>
   <si>
@@ -1719,9 +1512,6 @@
     <t>BSG 55-225-004</t>
   </si>
   <si>
-    <t>22714</t>
-  </si>
-  <si>
     <t>07040485</t>
   </si>
   <si>
@@ -1731,9 +1521,6 @@
     <t>BSG 55-225-002</t>
   </si>
   <si>
-    <t>26715</t>
-  </si>
-  <si>
     <t>DB4249</t>
   </si>
   <si>
@@ -1758,9 +1545,6 @@
     <t>94036700</t>
   </si>
   <si>
-    <t>32716</t>
-  </si>
-  <si>
     <t>DB4233</t>
   </si>
   <si>
@@ -1779,9 +1563,6 @@
     <t>BSG 83-225-002</t>
   </si>
   <si>
-    <t>34717</t>
-  </si>
-  <si>
     <t>14.4785.10</t>
   </si>
   <si>
@@ -1800,9 +1581,6 @@
     <t>BSG 85-225-005</t>
   </si>
   <si>
-    <t>34718</t>
-  </si>
-  <si>
     <t>14.D636.10</t>
   </si>
   <si>
@@ -1824,9 +1602,6 @@
     <t>94038600</t>
   </si>
   <si>
-    <t>34719</t>
-  </si>
-  <si>
     <t>DB7036</t>
   </si>
   <si>
@@ -1851,9 +1626,6 @@
     <t>94038800</t>
   </si>
   <si>
-    <t>34720</t>
-  </si>
-  <si>
     <t>14.9378.10</t>
   </si>
   <si>
@@ -1872,9 +1644,6 @@
     <t>94029300</t>
   </si>
   <si>
-    <t>34722</t>
-  </si>
-  <si>
     <t>14.9379.10</t>
   </si>
   <si>
@@ -1908,9 +1677,6 @@
     <t>4243105020</t>
   </si>
   <si>
-    <t>15723</t>
-  </si>
-  <si>
     <t>14.7739.10</t>
   </si>
   <si>
@@ -1944,9 +1710,6 @@
     <t>42610S70000</t>
   </si>
   <si>
-    <t>25728</t>
-  </si>
-  <si>
     <t>DB4408</t>
   </si>
   <si>
@@ -1977,9 +1740,6 @@
     <t>MB895470</t>
   </si>
   <si>
-    <t>32734</t>
-  </si>
-  <si>
     <t>14.9388.10</t>
   </si>
   <si>
@@ -2010,9 +1770,6 @@
     <t>BSG 83-225-001</t>
   </si>
   <si>
-    <t>32735</t>
-  </si>
-  <si>
     <t>DB4362</t>
   </si>
   <si>
@@ -2040,9 +1797,6 @@
     <t>94026500</t>
   </si>
   <si>
-    <t>34739</t>
-  </si>
-  <si>
     <t>DB4339</t>
   </si>
   <si>
@@ -2067,12 +1821,6 @@
     <t>424310D010</t>
   </si>
   <si>
-    <t>37737</t>
-  </si>
-  <si>
-    <t>27762</t>
-  </si>
-  <si>
     <t>DB4302</t>
   </si>
   <si>
@@ -2103,9 +1851,6 @@
     <t>94024200</t>
   </si>
   <si>
-    <t>30777</t>
-  </si>
-  <si>
     <t>14.5591.10</t>
   </si>
   <si>
@@ -2127,9 +1872,6 @@
     <t>94013700</t>
   </si>
   <si>
-    <t>33783</t>
-  </si>
-  <si>
     <t>14.7260.10</t>
   </si>
   <si>
@@ -2142,9 +1884,6 @@
     <t>94020000</t>
   </si>
   <si>
-    <t>16789</t>
-  </si>
-  <si>
     <t>DB4225</t>
   </si>
   <si>
@@ -2166,9 +1905,6 @@
     <t>94034900</t>
   </si>
   <si>
-    <t>16790</t>
-  </si>
-  <si>
     <t>BD-5188</t>
   </si>
   <si>
@@ -2184,9 +1920,6 @@
     <t>94046700</t>
   </si>
   <si>
-    <t>42804</t>
-  </si>
-  <si>
     <t>07050066</t>
   </si>
   <si>
@@ -2199,9 +1932,6 @@
     <t>6R0609617B</t>
   </si>
   <si>
-    <t>36815</t>
-  </si>
-  <si>
     <t>BF558</t>
   </si>
   <si>
@@ -2226,9 +1956,6 @@
     <t>2H0609617</t>
   </si>
   <si>
-    <t>30819</t>
-  </si>
-  <si>
     <t>14.5493.10</t>
   </si>
   <si>
@@ -2238,9 +1965,6 @@
     <t>BSG 75-225-005</t>
   </si>
   <si>
-    <t>31820</t>
-  </si>
-  <si>
     <t>14.9386.10</t>
   </si>
   <si>
@@ -2259,9 +1983,6 @@
     <t>1J0609617B</t>
   </si>
   <si>
-    <t>33824</t>
-  </si>
-  <si>
     <t>14.6755.10</t>
   </si>
   <si>
@@ -2277,9 +1998,6 @@
     <t>94014800</t>
   </si>
   <si>
-    <t>29825</t>
-  </si>
-  <si>
     <t>14.7093.10</t>
   </si>
   <si>
@@ -2289,9 +2007,6 @@
     <t>94014200</t>
   </si>
   <si>
-    <t>29826</t>
-  </si>
-  <si>
     <t>AD5113</t>
   </si>
   <si>
@@ -2301,9 +2016,6 @@
     <t>94028200</t>
   </si>
   <si>
-    <t>33827</t>
-  </si>
-  <si>
     <t>14.3157.10</t>
   </si>
   <si>
@@ -2319,9 +2031,6 @@
     <t>85015914</t>
   </si>
   <si>
-    <t>18911</t>
-  </si>
-  <si>
     <t>AD1109</t>
   </si>
   <si>
@@ -2331,9 +2040,6 @@
     <t>RAI-KD02041</t>
   </si>
   <si>
-    <t>33976</t>
-  </si>
-  <si>
     <t>14.3161.10</t>
   </si>
   <si>
@@ -2346,15 +2052,9 @@
     <t>94010200</t>
   </si>
   <si>
-    <t>33987</t>
-  </si>
-  <si>
     <t>14.3157.20</t>
   </si>
   <si>
-    <t>28988</t>
-  </si>
-  <si>
     <t>BFR484</t>
   </si>
   <si>
@@ -2367,9 +2067,6 @@
     <t>45387H</t>
   </si>
   <si>
-    <t>33992</t>
-  </si>
-  <si>
     <t>DB4563</t>
   </si>
   <si>
@@ -2382,24 +2079,15 @@
     <t>BDK300 33392</t>
   </si>
   <si>
-    <t>30997</t>
-  </si>
-  <si>
     <t>AD1132</t>
   </si>
   <si>
     <t>07050096</t>
   </si>
   <si>
-    <t>161065</t>
-  </si>
-  <si>
     <t>07050084</t>
   </si>
   <si>
-    <t>291066</t>
-  </si>
-  <si>
     <t>251919</t>
   </si>
   <si>
@@ -2415,45 +2103,24 @@
     <t>424759</t>
   </si>
   <si>
-    <t>63999</t>
-  </si>
-  <si>
     <t>3302350207001, 33023502070</t>
   </si>
   <si>
-    <t>251070</t>
-  </si>
-  <si>
     <t>MC862229</t>
   </si>
   <si>
-    <t>401071</t>
-  </si>
-  <si>
     <t>8970339891, 8941010571</t>
   </si>
   <si>
-    <t>401072</t>
-  </si>
-  <si>
     <t>8941010571</t>
   </si>
   <si>
-    <t>401073</t>
-  </si>
-  <si>
     <t>8973341070AA, 8973341070</t>
   </si>
   <si>
-    <t>341074</t>
-  </si>
-  <si>
     <t>14.4739.10</t>
   </si>
   <si>
-    <t>251075</t>
-  </si>
-  <si>
     <t>AD1159</t>
   </si>
   <si>
@@ -2463,9 +2130,6 @@
     <t>MK321338</t>
   </si>
   <si>
-    <t>321081</t>
-  </si>
-  <si>
     <t>DB4421</t>
   </si>
   <si>
@@ -2475,9 +2139,6 @@
     <t>94037800</t>
   </si>
   <si>
-    <t>191082</t>
-  </si>
-  <si>
     <t>14.7079.10</t>
   </si>
   <si>
@@ -2490,18 +2151,9 @@
     <t>94015600</t>
   </si>
   <si>
-    <t>341083</t>
-  </si>
-  <si>
     <t>4243137080</t>
   </si>
   <si>
-    <t>341084</t>
-  </si>
-  <si>
-    <t>131085</t>
-  </si>
-  <si>
     <t>14.7098.20</t>
   </si>
   <si>
@@ -2511,42 +2163,21 @@
     <t>BSG 30-225-005</t>
   </si>
   <si>
-    <t>131086</t>
-  </si>
-  <si>
     <t>AD5110</t>
   </si>
   <si>
     <t>07050093</t>
   </si>
   <si>
-    <t>341087</t>
-  </si>
-  <si>
     <t>14.E277.10</t>
   </si>
   <si>
     <t>30997B</t>
   </si>
   <si>
-    <t>251088</t>
-  </si>
-  <si>
-    <t>511089</t>
-  </si>
-  <si>
-    <t>261090</t>
-  </si>
-  <si>
-    <t>261091</t>
-  </si>
-  <si>
     <t>94026900</t>
   </si>
   <si>
-    <t>341092</t>
-  </si>
-  <si>
     <t>94045200</t>
   </si>
   <si>
@@ -3355,6 +2986,18 @@
   </si>
   <si>
     <t>OE_10</t>
+  </si>
+  <si>
+    <t>P90005YP, P90005</t>
+  </si>
+  <si>
+    <t>584114E000, OEK584114E000</t>
+  </si>
+  <si>
+    <t>432004334R, 432007629R, 432000978R</t>
+  </si>
+  <si>
+    <t>R2X61126AAN, R2X61126AA, 2660440</t>
   </si>
 </sst>
 </file>
@@ -3445,7 +3088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3501,7 +3144,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3510,17 +3152,28 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3840,23 +3493,23 @@
   <sheetFormatPr defaultColWidth="22.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="7.21875" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="9" max="10" width="9.77734375" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" customWidth="1"/>
+    <col min="16" max="16" width="19.44140625" customWidth="1"/>
     <col min="17" max="17" width="13.88671875" customWidth="1"/>
-    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="17.5546875" customWidth="1"/>
     <col min="20" max="20" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.77734375" bestFit="1" customWidth="1"/>
@@ -3870,7 +3523,7 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>838</v>
+        <v>715</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3885,13 +3538,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>849</v>
+        <v>726</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>842</v>
+        <v>719</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -3900,13 +3553,13 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>843</v>
+        <v>720</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>839</v>
+        <v>716</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>839</v>
+        <v>716</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>7</v>
@@ -3918,312 +3571,312 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>840</v>
+        <v>717</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>837</v>
+        <v>714</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="T1" s="27" t="s">
-        <v>1096</v>
-      </c>
-      <c r="U1" s="27" t="s">
-        <v>1097</v>
-      </c>
-      <c r="V1" s="27" t="s">
-        <v>1098</v>
-      </c>
-      <c r="W1" s="27" t="s">
-        <v>1099</v>
-      </c>
-      <c r="X1" s="27" t="s">
-        <v>1100</v>
-      </c>
-      <c r="Y1" s="27" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Z1" s="27" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AA1" s="27" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AB1" s="27" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AC1" s="27" t="s">
-        <v>1105</v>
+        <v>722</v>
+      </c>
+      <c r="T1" s="23" t="s">
+        <v>973</v>
+      </c>
+      <c r="U1" s="23" t="s">
+        <v>974</v>
+      </c>
+      <c r="V1" s="23" t="s">
+        <v>975</v>
+      </c>
+      <c r="W1" s="23" t="s">
+        <v>976</v>
+      </c>
+      <c r="X1" s="23" t="s">
+        <v>977</v>
+      </c>
+      <c r="Y1" s="23" t="s">
+        <v>978</v>
+      </c>
+      <c r="Z1" s="23" t="s">
+        <v>979</v>
+      </c>
+      <c r="AA1" s="23" t="s">
+        <v>980</v>
+      </c>
+      <c r="AB1" s="23" t="s">
+        <v>981</v>
+      </c>
+      <c r="AC1" s="23" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="29">
+        <v>24163</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="N2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="Q2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="T2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="18" t="s">
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A3" s="29">
+        <v>24165</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="N3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="T3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="16" t="s">
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A4" s="30">
+        <v>13275</v>
+      </c>
+      <c r="L4" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="18" t="s">
+      <c r="M4" s="20"/>
+      <c r="N4" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="T4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="L4" t="s">
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A5" s="29">
+        <v>13277</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="21"/>
-      <c r="N4" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="T4" s="21" t="s">
+      <c r="D5" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="J5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="L5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="M5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="Q5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="T5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="L5" t="s">
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A6" s="30">
+        <v>13278</v>
+      </c>
+      <c r="L6" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="13" t="s">
+      <c r="M6" s="20"/>
+      <c r="N6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="T6" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="18" t="s">
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A7" s="29">
+        <v>13279</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L7" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="21"/>
-      <c r="N6" s="13" t="s">
+      <c r="M7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="T6" s="21" t="s">
+      <c r="Q7" s="16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="T7" s="18" t="s">
+        <v>730</v>
+      </c>
+      <c r="U7" s="24" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A8" s="29">
+        <v>13280</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>721</v>
+      </c>
+      <c r="L8" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="M8" s="20"/>
+      <c r="N8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="T8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="L7" t="s">
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A9" s="29">
+        <v>13281</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="13" t="s">
+      <c r="C9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="18" t="s">
-        <v>853</v>
-      </c>
-      <c r="U7" s="28" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="J9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>844</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="K9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="21"/>
-      <c r="N8" s="13" t="s">
+      <c r="L9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="T8" s="18" t="s">
+      <c r="M9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="Q9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="T9" s="18" t="s">
+        <v>732</v>
+      </c>
+      <c r="U9" s="24" t="s">
+        <v>733</v>
+      </c>
+      <c r="V9" s="24" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A10" s="29">
+        <v>13282</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L10" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M10" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N10" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="T9" s="18" t="s">
-        <v>855</v>
-      </c>
-      <c r="U9" s="28" t="s">
-        <v>856</v>
-      </c>
-      <c r="V9" s="28" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="T10" s="18" t="s">
+        <v>735</v>
+      </c>
+      <c r="U10" s="24" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A11" s="29">
+        <v>13283</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="F11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="K11" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="L11" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="M11" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="Q11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="T10" s="18" t="s">
-        <v>858</v>
-      </c>
-      <c r="U10" s="28" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>75</v>
-      </c>
       <c r="T11" s="18" t="s">
-        <v>860</v>
-      </c>
-      <c r="U11" s="28" t="s">
-        <v>861</v>
-      </c>
-      <c r="V11" s="28" t="s">
-        <v>862</v>
+        <v>737</v>
+      </c>
+      <c r="U11" s="24" t="s">
+        <v>738</v>
+      </c>
+      <c r="V11" s="24" t="s">
+        <v>739</v>
       </c>
       <c r="W11">
         <v>1011288</v>
@@ -4232,157 +3885,157 @@
         <v>7296355</v>
       </c>
       <c r="Y11" t="s">
-        <v>863</v>
+        <v>740</v>
       </c>
       <c r="Z11" t="s">
-        <v>864</v>
+        <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="30">
+        <v>13284</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="T12" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A13" s="29">
+        <v>13285</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="L12" t="s">
+      <c r="R13" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="T12" s="21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="M13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>89</v>
       </c>
       <c r="S13" s="18"/>
       <c r="T13" s="18" t="s">
-        <v>865</v>
-      </c>
-      <c r="U13" s="28" t="s">
-        <v>866</v>
-      </c>
-      <c r="V13" s="28" t="s">
-        <v>867</v>
+        <v>742</v>
+      </c>
+      <c r="U13" s="24" t="s">
+        <v>743</v>
+      </c>
+      <c r="V13" s="24" t="s">
+        <v>744</v>
       </c>
       <c r="W13">
         <v>4519396</v>
       </c>
       <c r="X13" t="s">
-        <v>868</v>
+        <v>745</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>90</v>
+      <c r="A14" s="29">
+        <v>13286</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="S14" s="18"/>
       <c r="T14" s="18" t="s">
-        <v>869</v>
-      </c>
-      <c r="U14" s="28" t="s">
-        <v>870</v>
-      </c>
-      <c r="V14" s="28" t="s">
-        <v>871</v>
+        <v>746</v>
+      </c>
+      <c r="U14" s="24" t="s">
+        <v>747</v>
+      </c>
+      <c r="V14" s="24" t="s">
+        <v>748</v>
       </c>
       <c r="W14">
         <v>4041430</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>98</v>
+      <c r="A15" s="29">
+        <v>13290</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="S15" s="18"/>
       <c r="T15" s="18" t="s">
-        <v>872</v>
-      </c>
-      <c r="U15" s="28" t="s">
-        <v>873</v>
-      </c>
-      <c r="V15" s="28" t="s">
-        <v>874</v>
+        <v>749</v>
+      </c>
+      <c r="U15" s="24" t="s">
+        <v>750</v>
+      </c>
+      <c r="V15" s="24" t="s">
+        <v>751</v>
       </c>
       <c r="W15">
         <v>4367103</v>
@@ -4394,285 +4047,285 @@
         <v>1361304</v>
       </c>
       <c r="Z15" t="s">
-        <v>875</v>
+        <v>752</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>106</v>
+      <c r="A16" s="29">
+        <v>13289</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="S16" s="18"/>
       <c r="T16" s="18" t="s">
-        <v>876</v>
-      </c>
-      <c r="U16" s="28" t="s">
-        <v>877</v>
-      </c>
-      <c r="V16" s="28" t="s">
-        <v>878</v>
+        <v>753</v>
+      </c>
+      <c r="U16" s="24" t="s">
+        <v>754</v>
+      </c>
+      <c r="V16" s="24" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>112</v>
+      <c r="A17" s="29">
+        <v>36020</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="P17" s="15" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="Q17" s="16" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="S17" s="18"/>
       <c r="T17" s="18" t="s">
-        <v>879</v>
-      </c>
-      <c r="U17" s="28" t="s">
-        <v>880</v>
-      </c>
-      <c r="V17" s="28" t="s">
-        <v>881</v>
+        <v>756</v>
+      </c>
+      <c r="U17" s="24" t="s">
+        <v>757</v>
+      </c>
+      <c r="V17" s="24" t="s">
+        <v>758</v>
       </c>
       <c r="W17" t="s">
-        <v>882</v>
+        <v>759</v>
       </c>
       <c r="X17" t="s">
-        <v>883</v>
+        <v>760</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="29">
+        <v>25181</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A19" s="29">
+        <v>18160</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="P19" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>761</v>
+      </c>
+      <c r="U19" s="24" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A20" s="29">
+        <v>16183</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="L20" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="M20" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="N20" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="P20" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="L18" s="18" t="s">
+      <c r="Q20" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="M18" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="N18" s="13" t="s">
+      <c r="T20" s="18" t="s">
+        <v>763</v>
+      </c>
+      <c r="U20" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="V20" s="24" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A21" s="29">
+        <v>33149</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="P18" s="15" t="s">
+      <c r="C21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="16" t="s">
+      <c r="D21" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="T18" s="18" t="s">
+      <c r="E21" s="6" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="J21" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="K21" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="L21" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="M21" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="N21" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="M19" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="N19" s="13" t="s">
+      <c r="O21" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="O19" s="14" t="s">
+      <c r="R21" s="17" t="s">
         <v>140</v>
-      </c>
-      <c r="P19" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q19" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>884</v>
-      </c>
-      <c r="U19" s="28" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q20" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="T20" s="18" t="s">
-        <v>886</v>
-      </c>
-      <c r="U20" s="28" t="s">
-        <v>887</v>
-      </c>
-      <c r="V20" s="28" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="M21" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="O21" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="R21" s="17" t="s">
-        <v>160</v>
       </c>
       <c r="S21" s="18"/>
       <c r="T21" s="18" t="s">
-        <v>889</v>
-      </c>
-      <c r="U21" s="28" t="s">
-        <v>890</v>
+        <v>766</v>
+      </c>
+      <c r="U21" s="24" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>161</v>
+      <c r="A22" s="29">
+        <v>40217</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="P22" s="15" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="Q22" s="16" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="T22" s="18" t="s">
-        <v>891</v>
-      </c>
-      <c r="U22" s="28" t="s">
-        <v>892</v>
-      </c>
-      <c r="V22" s="28" t="s">
-        <v>893</v>
+        <v>768</v>
+      </c>
+      <c r="U22" s="24" t="s">
+        <v>769</v>
+      </c>
+      <c r="V22" s="24" t="s">
+        <v>770</v>
       </c>
       <c r="W22">
         <v>94226829</v>
@@ -4692,220 +4345,220 @@
       <c r="AB22">
         <v>8979128660</v>
       </c>
-      <c r="AC22" s="28" t="s">
-        <v>1095</v>
+      <c r="AC22" s="24" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>169</v>
+      <c r="A23" s="29">
+        <v>28324</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="S23" s="18"/>
       <c r="T23" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A24" s="29">
+        <v>36349</v>
+      </c>
+      <c r="C24" t="s">
+        <v>729</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="T24" s="18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A25" s="29">
+        <v>40371</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="P25" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="T25" s="18" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A26" s="29">
+        <v>40372</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="P26" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="T26" s="18" t="s">
+        <v>771</v>
+      </c>
+      <c r="U26" s="24" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A27" s="29">
+        <v>27381</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="L27" t="s">
         <v>181</v>
       </c>
-      <c r="C24" t="s">
-        <v>852</v>
-      </c>
-      <c r="N24" s="13" t="s">
+      <c r="M27" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="N27" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="Q24" s="16" t="s">
+      <c r="O27" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="T24" s="18" t="s">
+      <c r="R27" s="17" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="P25" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q25" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="T25" s="18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="N26" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="O26" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="P26" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q26" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="T26" s="18" t="s">
-        <v>894</v>
-      </c>
-      <c r="U26" s="28" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="L27" t="s">
-        <v>207</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="N27" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="O27" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="R27" s="17" t="s">
-        <v>210</v>
       </c>
       <c r="S27" s="18"/>
       <c r="T27" s="18" t="s">
-        <v>896</v>
-      </c>
-      <c r="U27" s="28" t="s">
-        <v>897</v>
+        <v>773</v>
+      </c>
+      <c r="U27" s="24" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>211</v>
+      <c r="A28" s="29">
+        <v>27382</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="O28" s="14" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="Q28" s="16" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="T28" s="18" t="s">
-        <v>898</v>
-      </c>
-      <c r="U28" s="28" t="s">
-        <v>899</v>
-      </c>
-      <c r="V28" s="28" t="s">
-        <v>900</v>
+        <v>775</v>
+      </c>
+      <c r="U28" s="24" t="s">
+        <v>776</v>
+      </c>
+      <c r="V28" s="24" t="s">
+        <v>777</v>
       </c>
       <c r="W28">
         <v>91024352</v>
@@ -4924,786 +4577,786 @@
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>222</v>
+      <c r="A29" s="29">
+        <v>27383</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="Q29" s="16" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>901</v>
-      </c>
-      <c r="U29" s="28" t="s">
-        <v>902</v>
-      </c>
-      <c r="V29" s="28" t="s">
-        <v>903</v>
+        <v>778</v>
+      </c>
+      <c r="U29" s="24" t="s">
+        <v>779</v>
+      </c>
+      <c r="V29" s="24" t="s">
+        <v>780</v>
       </c>
       <c r="W29">
         <v>90193915</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>232</v>
+      <c r="A30" s="29">
+        <v>27384</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="L30" s="18" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="Q30" s="16" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="S30" s="18"/>
       <c r="T30" s="18" t="s">
-        <v>904</v>
-      </c>
-      <c r="U30" s="28" t="s">
-        <v>905</v>
-      </c>
-      <c r="V30" s="28" t="s">
-        <v>906</v>
+        <v>781</v>
+      </c>
+      <c r="U30" s="24" t="s">
+        <v>782</v>
+      </c>
+      <c r="V30" s="24" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="30">
+        <v>45387</v>
+      </c>
+      <c r="M31" s="21"/>
+      <c r="N31" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="T31" s="20" t="s">
+        <v>784</v>
+      </c>
+      <c r="U31" s="24" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A32" s="30">
+        <v>45396</v>
+      </c>
+      <c r="M32" s="21"/>
+      <c r="N32" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="T32" s="20" t="s">
+        <v>786</v>
+      </c>
+      <c r="U32" s="24" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" s="29">
+        <v>25412</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q33" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="T33" s="18" t="s">
+        <v>788</v>
+      </c>
+      <c r="U33" s="24" t="s">
+        <v>789</v>
+      </c>
+      <c r="V33" s="24" t="s">
+        <v>790</v>
+      </c>
+      <c r="W33" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="M34" s="21"/>
+      <c r="N34" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="T34" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A35" s="29">
+        <v>28431</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="T35" s="18" t="s">
+        <v>792</v>
+      </c>
+      <c r="U35" s="24" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A36" s="29">
+        <v>51435</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="N36" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="T36" s="18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A37" s="29">
+        <v>27447</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="O37" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="M31" s="22"/>
-      <c r="N31" s="13" t="s">
+      <c r="Q37" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="T31" s="21" t="s">
-        <v>907</v>
-      </c>
-      <c r="U31" s="28" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="M32" s="22"/>
-      <c r="N32" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="T32" s="21" t="s">
-        <v>909</v>
-      </c>
-      <c r="U32" s="28" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="M33" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="N33" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="O33" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="P33" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q33" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="T33" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="U33" s="28" t="s">
-        <v>912</v>
-      </c>
-      <c r="V33" s="28" t="s">
-        <v>913</v>
-      </c>
-      <c r="W33" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="M34" s="22"/>
-      <c r="N34" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="T34" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="M35" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="N35" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="T35" s="18" t="s">
-        <v>915</v>
-      </c>
-      <c r="U35" s="28" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="N36" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="P36" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="T36" s="18" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="L37" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="M37" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="N37" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="O37" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q37" s="16" t="s">
-        <v>279</v>
-      </c>
       <c r="R37" s="17" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="S37" s="18"/>
       <c r="T37" s="18" t="s">
-        <v>917</v>
-      </c>
-      <c r="U37" s="28" t="s">
-        <v>918</v>
+        <v>794</v>
+      </c>
+      <c r="U37" s="24" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>281</v>
+      <c r="A38" s="29">
+        <v>27448</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="L38" s="18" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="Q38" s="16" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="R38" s="17" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="S38" s="18"/>
       <c r="T38" s="18" t="s">
-        <v>919</v>
-      </c>
-      <c r="U38" s="28" t="s">
-        <v>920</v>
-      </c>
-      <c r="V38" s="28" t="s">
-        <v>921</v>
+        <v>796</v>
+      </c>
+      <c r="U38" s="24" t="s">
+        <v>797</v>
+      </c>
+      <c r="V38" s="24" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="29">
+        <v>18455</v>
+      </c>
+      <c r="F39" s="20"/>
+      <c r="L39" t="s">
+        <v>256</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="S39" s="22" t="s">
+        <v>723</v>
+      </c>
+      <c r="T39" s="18" t="s">
+        <v>799</v>
+      </c>
+      <c r="U39" s="24" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40" s="29">
+        <v>26463</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="T40" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" s="30">
+        <v>45473</v>
+      </c>
+      <c r="M41" s="21"/>
+      <c r="N41" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="T41" s="21"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A42" s="29">
+        <v>59480</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="L42" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="T42" s="18" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A43" s="29">
+        <v>27504</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="O43" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q43" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="T43" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44" s="29">
+        <v>16508</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="L44" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="M44" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="O44" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="P44" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q44" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="T44" s="18" t="s">
+        <v>801</v>
+      </c>
+      <c r="U44" s="24" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="29">
+        <v>25509</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="N45" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="O45" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="P45" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="F39" s="21"/>
-      <c r="L39" t="s">
+      <c r="Q45" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="M39" s="21"/>
-      <c r="N39" s="13" t="s">
+      <c r="R45" s="17" t="s">
         <v>294</v>
-      </c>
-      <c r="S39" s="23" t="s">
-        <v>846</v>
-      </c>
-      <c r="T39" s="18" t="s">
-        <v>922</v>
-      </c>
-      <c r="U39" s="28" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="M40" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="N40" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="P40" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="T40" s="18" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="M41" s="22"/>
-      <c r="N41" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="T41" s="22"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="K42" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="M42" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="N42" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="T42" s="18" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="O43" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q43" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="T43" s="18" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="M44" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="O44" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="P44" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q44" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="T44" s="18" t="s">
-        <v>924</v>
-      </c>
-      <c r="U44" s="28" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="L45" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="M45" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="N45" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="O45" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="P45" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q45" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="R45" s="17" t="s">
-        <v>337</v>
       </c>
       <c r="S45" s="18"/>
       <c r="T45" s="18" t="s">
-        <v>926</v>
-      </c>
-      <c r="U45" s="28" t="s">
-        <v>927</v>
-      </c>
-      <c r="V45" s="28" t="s">
-        <v>928</v>
+        <v>803</v>
+      </c>
+      <c r="U45" s="24" t="s">
+        <v>804</v>
+      </c>
+      <c r="V45" s="24" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>338</v>
+      <c r="A46" s="29">
+        <v>16518</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="L46" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="M46" s="20" t="s">
-        <v>342</v>
+        <v>298</v>
+      </c>
+      <c r="M46" s="19" t="s">
+        <v>298</v>
       </c>
       <c r="N46" s="13" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="P46" s="15" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="Q46" s="16" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="T46" s="18" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>347</v>
+      <c r="A47" s="29">
+        <v>59519</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>348</v>
+        <v>303</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="M47" s="12" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="N47" s="13" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="T47" s="18" t="s">
-        <v>351</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>352</v>
+      <c r="A48" s="29">
+        <v>36532</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="O48" s="14" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="Q48" s="16" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
       <c r="R48" s="17" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="S48" s="18"/>
       <c r="T48" s="18" t="s">
-        <v>929</v>
-      </c>
-      <c r="U48" s="28" t="s">
-        <v>930</v>
-      </c>
-      <c r="V48" s="28" t="s">
-        <v>931</v>
+        <v>806</v>
+      </c>
+      <c r="U48" s="24" t="s">
+        <v>807</v>
+      </c>
+      <c r="V48" s="24" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>365</v>
+      <c r="A49" s="29">
+        <v>13544</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>366</v>
+        <v>319</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
       <c r="M49" s="12" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
       <c r="N49" s="13" t="s">
-        <v>369</v>
+        <v>322</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
       <c r="Q49" s="16" t="s">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="R49" s="17" t="s">
-        <v>372</v>
+        <v>325</v>
       </c>
       <c r="S49" s="18"/>
       <c r="T49" s="18" t="s">
-        <v>932</v>
-      </c>
-      <c r="U49" s="28" t="s">
-        <v>933</v>
+        <v>809</v>
+      </c>
+      <c r="U49" s="24" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>373</v>
+      <c r="A50" s="29">
+        <v>16561</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>375</v>
+        <v>327</v>
       </c>
       <c r="L50" s="18" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>377</v>
+        <v>329</v>
       </c>
       <c r="O50" s="14" t="s">
-        <v>378</v>
+        <v>330</v>
       </c>
       <c r="P50" s="15" t="s">
-        <v>379</v>
+        <v>331</v>
       </c>
       <c r="Q50" s="16" t="s">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="R50" s="17" t="s">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="S50" s="18"/>
       <c r="T50" s="18" t="s">
-        <v>934</v>
-      </c>
-      <c r="U50" s="28" t="s">
-        <v>935</v>
+        <v>811</v>
+      </c>
+      <c r="U50" s="24" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>382</v>
+      <c r="A51" s="29">
+        <v>34565</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>386</v>
+        <v>337</v>
       </c>
       <c r="L51" s="18" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="O51" s="14" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="P51" s="15" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="Q51" s="16" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="T51" s="18" t="s">
-        <v>936</v>
-      </c>
-      <c r="U51" s="28" t="s">
-        <v>937</v>
-      </c>
-      <c r="V51" s="28" t="s">
-        <v>938</v>
+        <v>813</v>
+      </c>
+      <c r="U51" s="24" t="s">
+        <v>814</v>
+      </c>
+      <c r="V51" s="24" t="s">
+        <v>815</v>
       </c>
       <c r="W51">
         <v>94852720</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>391</v>
+      <c r="A52" s="29">
+        <v>40569</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>392</v>
+        <v>342</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>395</v>
+        <v>345</v>
       </c>
       <c r="L52" s="18" t="s">
-        <v>396</v>
+        <v>346</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>396</v>
+        <v>346</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="P52" s="15" t="s">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="Q52" s="16" t="s">
-        <v>398</v>
+        <v>348</v>
       </c>
       <c r="R52" s="17" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="S52" s="18"/>
       <c r="T52" s="18" t="s">
-        <v>939</v>
-      </c>
-      <c r="U52" s="28" t="s">
-        <v>940</v>
-      </c>
-      <c r="V52" s="28" t="s">
-        <v>941</v>
+        <v>816</v>
+      </c>
+      <c r="U52" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V52" s="24" t="s">
+        <v>818</v>
       </c>
       <c r="W52">
         <v>8980618131</v>
@@ -5719,116 +5372,116 @@
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>400</v>
+      <c r="A53" s="29">
+        <v>36571</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="L53" s="18" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="M53" s="12" t="s">
-        <v>406</v>
+        <v>355</v>
       </c>
       <c r="Q53" s="16" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="R53" s="17" t="s">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="S53" s="18"/>
       <c r="T53" s="18" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>410</v>
+      <c r="A54" s="29">
+        <v>30579</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>411</v>
+        <v>359</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="L54" s="18" t="s">
-        <v>414</v>
+        <v>362</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>414</v>
+        <v>362</v>
       </c>
       <c r="O54" s="14" t="s">
-        <v>415</v>
+        <v>363</v>
       </c>
       <c r="Q54" s="16" t="s">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="T54" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="U54" s="28" t="s">
-        <v>943</v>
+        <v>819</v>
+      </c>
+      <c r="U54" s="24" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>417</v>
+      <c r="A55" s="29">
+        <v>33591</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>418</v>
+        <v>365</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>422</v>
+        <v>369</v>
       </c>
       <c r="L55" s="18" t="s">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="M55" s="12" t="s">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="O55" s="14" t="s">
-        <v>424</v>
+        <v>371</v>
       </c>
       <c r="Q55" s="16" t="s">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="R55" s="17" t="s">
-        <v>426</v>
+        <v>373</v>
       </c>
       <c r="S55" s="18"/>
       <c r="T55" s="18" t="s">
-        <v>944</v>
-      </c>
-      <c r="U55" s="28" t="s">
-        <v>945</v>
-      </c>
-      <c r="V55" s="28" t="s">
-        <v>946</v>
+        <v>821</v>
+      </c>
+      <c r="U55" s="24" t="s">
+        <v>822</v>
+      </c>
+      <c r="V55" s="24" t="s">
+        <v>823</v>
       </c>
       <c r="W55">
         <v>568270</v>
@@ -5836,1275 +5489,1275 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="L56" s="18" t="s">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="N56" s="13" t="s">
-        <v>430</v>
+        <v>377</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>431</v>
+        <v>378</v>
       </c>
       <c r="R56" s="17" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="S56" s="18"/>
       <c r="T56" s="18" t="s">
-        <v>942</v>
-      </c>
-      <c r="U56" s="28" t="s">
-        <v>943</v>
+        <v>819</v>
+      </c>
+      <c r="U56" s="24" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>433</v>
+      <c r="A57" s="29">
+        <v>28593</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="L57" s="18" t="s">
-        <v>437</v>
+        <v>383</v>
       </c>
       <c r="M57" s="12" t="s">
-        <v>437</v>
+        <v>383</v>
       </c>
       <c r="T57" s="18" t="s">
-        <v>947</v>
-      </c>
-      <c r="U57" s="28" t="s">
-        <v>948</v>
+        <v>824</v>
+      </c>
+      <c r="U57" s="24" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>438</v>
+      <c r="A58" s="29">
+        <v>33740</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>439</v>
+        <v>384</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>440</v>
+        <v>385</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>441</v>
+        <v>386</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>444</v>
+        <v>389</v>
       </c>
       <c r="L58" s="18" t="s">
-        <v>445</v>
+        <v>390</v>
       </c>
       <c r="M58" s="12" t="s">
-        <v>445</v>
+        <v>390</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="Q58" s="16" t="s">
-        <v>447</v>
+        <v>392</v>
       </c>
       <c r="R58" s="17" t="s">
-        <v>448</v>
+        <v>393</v>
       </c>
       <c r="S58" s="18"/>
       <c r="T58" s="18" t="s">
-        <v>949</v>
-      </c>
-      <c r="U58" s="28" t="s">
-        <v>950</v>
-      </c>
-      <c r="V58" s="28" t="s">
-        <v>951</v>
+        <v>826</v>
+      </c>
+      <c r="U58" s="24" t="s">
+        <v>827</v>
+      </c>
+      <c r="V58" s="24" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>449</v>
+      <c r="A59" s="29">
+        <v>26747</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>450</v>
+        <v>394</v>
       </c>
       <c r="L59" s="18" t="s">
-        <v>451</v>
+        <v>395</v>
       </c>
       <c r="M59" s="12" t="s">
-        <v>451</v>
+        <v>395</v>
       </c>
       <c r="P59" s="15" t="s">
-        <v>452</v>
+        <v>396</v>
       </c>
       <c r="Q59" s="16" t="s">
-        <v>453</v>
+        <v>397</v>
       </c>
       <c r="R59" s="17" t="s">
-        <v>454</v>
+        <v>398</v>
       </c>
       <c r="S59" s="18"/>
       <c r="T59" s="18" t="s">
-        <v>455</v>
+        <v>399</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>456</v>
+      <c r="A60" s="29">
+        <v>15701</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>457</v>
+        <v>400</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="L60" t="s">
-        <v>461</v>
+        <v>404</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>461</v>
+        <v>404</v>
       </c>
       <c r="P60" s="15" t="s">
-        <v>462</v>
+        <v>405</v>
       </c>
       <c r="Q60" s="16" t="s">
-        <v>463</v>
+        <v>406</v>
       </c>
       <c r="T60" s="18" t="s">
-        <v>952</v>
-      </c>
-      <c r="U60" s="28" t="s">
-        <v>953</v>
-      </c>
-      <c r="V60" s="28" t="s">
-        <v>954</v>
+        <v>829</v>
+      </c>
+      <c r="U60" s="24" t="s">
+        <v>830</v>
+      </c>
+      <c r="V60" s="24" t="s">
+        <v>831</v>
       </c>
       <c r="W60" t="s">
-        <v>955</v>
+        <v>832</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>464</v>
+      <c r="A61" s="29">
+        <v>15702</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>465</v>
+        <v>407</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>466</v>
+        <v>408</v>
       </c>
       <c r="L61" s="18" t="s">
-        <v>467</v>
+        <v>409</v>
       </c>
       <c r="M61" s="12" t="s">
-        <v>467</v>
+        <v>409</v>
       </c>
       <c r="P61" s="15" t="s">
-        <v>468</v>
+        <v>410</v>
       </c>
       <c r="Q61" s="16" t="s">
-        <v>469</v>
+        <v>411</v>
       </c>
       <c r="R61" s="17" t="s">
-        <v>470</v>
+        <v>412</v>
       </c>
       <c r="S61" s="18"/>
       <c r="T61" s="18" t="s">
-        <v>471</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>472</v>
+      <c r="A62" s="29">
+        <v>16703</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>473</v>
+        <v>414</v>
       </c>
       <c r="L62" s="18" t="s">
-        <v>474</v>
-      </c>
-      <c r="M62" s="20" t="s">
-        <v>474</v>
+        <v>415</v>
+      </c>
+      <c r="M62" s="19" t="s">
+        <v>415</v>
       </c>
       <c r="P62" s="15" t="s">
-        <v>475</v>
+        <v>416</v>
       </c>
       <c r="T62" s="18" t="s">
-        <v>476</v>
+        <v>417</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>477</v>
+      <c r="A63" s="29">
+        <v>16704</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="L63" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="M63" s="20" t="s">
-        <v>479</v>
+        <v>419</v>
+      </c>
+      <c r="M63" s="19" t="s">
+        <v>419</v>
       </c>
       <c r="P63" s="15" t="s">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="Q63" s="16" t="s">
-        <v>481</v>
+        <v>421</v>
       </c>
       <c r="T63" s="18" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>483</v>
+      <c r="A64" s="29">
+        <v>16705</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>484</v>
+        <v>423</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>485</v>
+        <v>424</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>487</v>
+        <v>426</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>488</v>
+        <v>427</v>
       </c>
       <c r="L64" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="M64" s="20" t="s">
-        <v>489</v>
+        <v>428</v>
+      </c>
+      <c r="M64" s="19" t="s">
+        <v>428</v>
       </c>
       <c r="P64" s="15" t="s">
-        <v>490</v>
+        <v>429</v>
       </c>
       <c r="Q64" s="16" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="T64" s="18" t="s">
-        <v>492</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>493</v>
+      <c r="A65" s="29">
+        <v>16706</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>494</v>
+        <v>432</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>485</v>
+        <v>424</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>495</v>
+        <v>433</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>496</v>
+        <v>434</v>
       </c>
       <c r="L65" t="s">
-        <v>497</v>
-      </c>
-      <c r="M65" s="20" t="s">
-        <v>497</v>
+        <v>435</v>
+      </c>
+      <c r="M65" s="19" t="s">
+        <v>435</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>498</v>
+        <v>436</v>
       </c>
       <c r="P65" s="15" t="s">
-        <v>499</v>
+        <v>437</v>
       </c>
       <c r="Q65" s="16" t="s">
-        <v>500</v>
+        <v>438</v>
       </c>
       <c r="T65" s="18" t="s">
-        <v>956</v>
-      </c>
-      <c r="U65" s="28" t="s">
-        <v>957</v>
-      </c>
-      <c r="V65" s="28" t="s">
-        <v>958</v>
+        <v>833</v>
+      </c>
+      <c r="U65" s="24" t="s">
+        <v>834</v>
+      </c>
+      <c r="V65" s="24" t="s">
+        <v>835</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>501</v>
+      <c r="A66" s="29">
+        <v>16707</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>502</v>
+        <v>439</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>503</v>
+        <v>440</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>504</v>
+        <v>441</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>505</v>
+        <v>442</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>506</v>
+        <v>443</v>
       </c>
       <c r="L66" s="18" t="s">
-        <v>507</v>
+        <v>444</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>507</v>
+        <v>444</v>
       </c>
       <c r="P66" s="15" t="s">
-        <v>508</v>
+        <v>445</v>
       </c>
       <c r="T66" s="18" t="s">
-        <v>959</v>
-      </c>
-      <c r="U66" s="28" t="s">
-        <v>960</v>
+        <v>836</v>
+      </c>
+      <c r="U66" s="24" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>509</v>
+      <c r="A67" s="29">
+        <v>16708</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>510</v>
+        <v>446</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>511</v>
+        <v>447</v>
       </c>
       <c r="L67" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="M67" s="20" t="s">
-        <v>512</v>
+        <v>448</v>
+      </c>
+      <c r="M67" s="19" t="s">
+        <v>448</v>
       </c>
       <c r="P67" s="15" t="s">
-        <v>513</v>
+        <v>449</v>
       </c>
       <c r="Q67" s="16" t="s">
-        <v>514</v>
+        <v>450</v>
       </c>
       <c r="T67" s="18" t="s">
-        <v>515</v>
+        <v>451</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>516</v>
+      <c r="A68" s="29">
+        <v>16709</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>518</v>
+        <v>453</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>519</v>
+        <v>454</v>
       </c>
       <c r="L68" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="M68" s="20" t="s">
-        <v>520</v>
+        <v>455</v>
+      </c>
+      <c r="M68" s="19" t="s">
+        <v>455</v>
       </c>
       <c r="P68" s="15" t="s">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="Q68" s="16" t="s">
-        <v>522</v>
+        <v>457</v>
       </c>
       <c r="T68" s="18" t="s">
-        <v>961</v>
-      </c>
-      <c r="U68" s="28" t="s">
-        <v>962</v>
+        <v>838</v>
+      </c>
+      <c r="U68" s="24" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>523</v>
+      <c r="A69" s="29">
+        <v>16710</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>524</v>
+        <v>458</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>525</v>
+        <v>459</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>526</v>
+        <v>460</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>527</v>
+        <v>461</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="L69" s="18" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="M69" s="12" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>530</v>
+        <v>464</v>
       </c>
       <c r="P69" s="15" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="Q69" s="16" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="R69" s="17" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
       <c r="S69" s="18"/>
       <c r="T69" s="18" t="s">
-        <v>534</v>
+        <v>468</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>535</v>
+      <c r="A70" s="29">
+        <v>18711</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>536</v>
+        <v>469</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>537</v>
+        <v>470</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>538</v>
+        <v>471</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>539</v>
+        <v>472</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>540</v>
+        <v>473</v>
       </c>
       <c r="L70" s="18" t="s">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="M70" s="12" t="s">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="P70" s="15" t="s">
-        <v>542</v>
+        <v>475</v>
       </c>
       <c r="Q70" s="16" t="s">
-        <v>543</v>
+        <v>476</v>
       </c>
       <c r="T70" s="18" t="s">
-        <v>963</v>
-      </c>
-      <c r="U70" s="28" t="s">
-        <v>964</v>
-      </c>
-      <c r="V70" s="28" t="s">
-        <v>965</v>
+        <v>840</v>
+      </c>
+      <c r="U70" s="24" t="s">
+        <v>841</v>
+      </c>
+      <c r="V70" s="24" t="s">
+        <v>842</v>
       </c>
       <c r="W70" t="s">
-        <v>966</v>
+        <v>843</v>
       </c>
       <c r="X70" t="s">
-        <v>967</v>
+        <v>844</v>
       </c>
       <c r="Y70" t="s">
-        <v>968</v>
+        <v>845</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>544</v>
+      <c r="A71" s="29">
+        <v>22712</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>545</v>
+        <v>477</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>546</v>
+        <v>478</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>547</v>
+        <v>479</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>548</v>
+        <v>480</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>549</v>
+        <v>481</v>
       </c>
       <c r="M71" s="12" t="s">
-        <v>549</v>
+        <v>481</v>
       </c>
       <c r="P71" s="15" t="s">
-        <v>550</v>
+        <v>482</v>
       </c>
       <c r="Q71" s="16" t="s">
-        <v>551</v>
+        <v>483</v>
       </c>
       <c r="T71" s="18" t="s">
-        <v>969</v>
-      </c>
-      <c r="U71" s="28" t="s">
-        <v>970</v>
-      </c>
-      <c r="V71" s="28" t="s">
-        <v>971</v>
+        <v>846</v>
+      </c>
+      <c r="U71" s="24" t="s">
+        <v>847</v>
+      </c>
+      <c r="V71" s="24" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>552</v>
+      <c r="A72" s="29">
+        <v>22713</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>553</v>
+        <v>484</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>554</v>
+        <v>485</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>555</v>
+        <v>486</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>547</v>
+        <v>479</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>556</v>
+        <v>487</v>
       </c>
       <c r="L72" t="s">
-        <v>557</v>
+        <v>488</v>
       </c>
       <c r="M72" s="12" t="s">
-        <v>557</v>
+        <v>488</v>
       </c>
       <c r="P72" s="15" t="s">
-        <v>558</v>
+        <v>489</v>
       </c>
       <c r="Q72" s="16" t="s">
-        <v>559</v>
+        <v>490</v>
       </c>
       <c r="T72" s="18" t="s">
-        <v>972</v>
-      </c>
-      <c r="U72" s="28" t="s">
-        <v>973</v>
-      </c>
-      <c r="V72" s="28" t="s">
-        <v>974</v>
+        <v>849</v>
+      </c>
+      <c r="U72" s="24" t="s">
+        <v>850</v>
+      </c>
+      <c r="V72" s="24" t="s">
+        <v>851</v>
       </c>
       <c r="W72" t="s">
-        <v>975</v>
+        <v>852</v>
       </c>
       <c r="X72" t="s">
-        <v>976</v>
+        <v>853</v>
       </c>
       <c r="Y72" t="s">
-        <v>977</v>
+        <v>854</v>
       </c>
       <c r="Z72" t="s">
-        <v>978</v>
+        <v>855</v>
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>560</v>
+      <c r="A73" s="29">
+        <v>22714</v>
       </c>
       <c r="L73" t="s">
-        <v>561</v>
+        <v>491</v>
       </c>
       <c r="M73" s="12" t="s">
-        <v>561</v>
+        <v>491</v>
       </c>
       <c r="P73" s="15" t="s">
-        <v>562</v>
+        <v>492</v>
       </c>
       <c r="Q73" s="16" t="s">
-        <v>563</v>
+        <v>493</v>
       </c>
       <c r="T73" s="18" t="s">
-        <v>979</v>
-      </c>
-      <c r="U73" s="28" t="s">
-        <v>980</v>
-      </c>
-      <c r="V73" s="28" t="s">
-        <v>981</v>
+        <v>856</v>
+      </c>
+      <c r="U73" s="24" t="s">
+        <v>857</v>
+      </c>
+      <c r="V73" s="24" t="s">
+        <v>858</v>
       </c>
       <c r="W73" t="s">
-        <v>982</v>
+        <v>859</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>564</v>
+      <c r="A74" s="29">
+        <v>26715</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>565</v>
+        <v>494</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>566</v>
+        <v>495</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>567</v>
+        <v>496</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>568</v>
+        <v>497</v>
       </c>
       <c r="L74" s="18" t="s">
-        <v>569</v>
+        <v>498</v>
       </c>
       <c r="M74" s="12" t="s">
-        <v>569</v>
+        <v>498</v>
       </c>
       <c r="P74" s="15" t="s">
-        <v>570</v>
+        <v>499</v>
       </c>
       <c r="Q74" s="16" t="s">
-        <v>571</v>
+        <v>500</v>
       </c>
       <c r="R74" s="17" t="s">
-        <v>572</v>
+        <v>501</v>
       </c>
       <c r="S74" s="18"/>
       <c r="T74" s="18" t="s">
-        <v>983</v>
-      </c>
-      <c r="U74" s="28" t="s">
-        <v>984</v>
-      </c>
-      <c r="V74" s="28" t="s">
-        <v>985</v>
+        <v>860</v>
+      </c>
+      <c r="U74" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="V74" s="24" t="s">
+        <v>862</v>
       </c>
       <c r="W74" t="s">
-        <v>986</v>
+        <v>863</v>
       </c>
       <c r="X74" t="s">
-        <v>987</v>
+        <v>864</v>
       </c>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>573</v>
+      <c r="A75" s="29">
+        <v>32716</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>574</v>
+        <v>502</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>575</v>
+        <v>503</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>576</v>
+        <v>504</v>
       </c>
       <c r="L75" t="s">
-        <v>577</v>
+        <v>505</v>
       </c>
       <c r="M75" s="12" t="s">
-        <v>577</v>
+        <v>505</v>
       </c>
       <c r="P75" s="15" t="s">
-        <v>578</v>
+        <v>506</v>
       </c>
       <c r="Q75" s="16" t="s">
-        <v>579</v>
+        <v>507</v>
       </c>
       <c r="T75" s="18" t="s">
-        <v>988</v>
-      </c>
-      <c r="U75" s="28" t="s">
-        <v>989</v>
+        <v>865</v>
+      </c>
+      <c r="U75" s="24" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>580</v>
+      <c r="A76" s="29">
+        <v>34717</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>582</v>
+        <v>509</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>583</v>
+        <v>510</v>
       </c>
       <c r="L76" s="18" t="s">
-        <v>584</v>
+        <v>511</v>
       </c>
       <c r="M76" s="12" t="s">
-        <v>584</v>
+        <v>511</v>
       </c>
       <c r="P76" s="15" t="s">
-        <v>585</v>
+        <v>512</v>
       </c>
       <c r="Q76" s="16" t="s">
-        <v>586</v>
+        <v>513</v>
       </c>
       <c r="T76" s="18" t="s">
-        <v>990</v>
-      </c>
-      <c r="U76" s="28" t="s">
-        <v>991</v>
-      </c>
-      <c r="V76" s="28" t="s">
-        <v>992</v>
+        <v>867</v>
+      </c>
+      <c r="U76" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="V76" s="24" t="s">
+        <v>869</v>
       </c>
       <c r="W76">
         <v>4243135080</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>587</v>
+      <c r="A77" s="29">
+        <v>34718</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>588</v>
+        <v>514</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>589</v>
+        <v>515</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>590</v>
+        <v>516</v>
       </c>
       <c r="L77" s="18" t="s">
-        <v>591</v>
+        <v>517</v>
       </c>
       <c r="M77" s="12" t="s">
-        <v>591</v>
+        <v>517</v>
       </c>
       <c r="P77" s="15" t="s">
-        <v>592</v>
+        <v>518</v>
       </c>
       <c r="Q77" s="16" t="s">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="R77" s="17" t="s">
-        <v>594</v>
+        <v>520</v>
       </c>
       <c r="S77" s="18"/>
       <c r="T77" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="U77" s="28" t="s">
-        <v>994</v>
-      </c>
-      <c r="V77" s="28" t="s">
-        <v>995</v>
+        <v>870</v>
+      </c>
+      <c r="U77" s="24" t="s">
+        <v>871</v>
+      </c>
+      <c r="V77" s="24" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>595</v>
+      <c r="A78" s="29">
+        <v>34719</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>596</v>
+        <v>521</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>597</v>
+        <v>522</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>598</v>
+        <v>523</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>599</v>
+        <v>524</v>
       </c>
       <c r="L78" s="18" t="s">
-        <v>600</v>
+        <v>525</v>
       </c>
       <c r="M78" s="12" t="s">
-        <v>600</v>
+        <v>525</v>
       </c>
       <c r="P78" s="15" t="s">
-        <v>601</v>
+        <v>526</v>
       </c>
       <c r="Q78" s="16" t="s">
-        <v>602</v>
+        <v>527</v>
       </c>
       <c r="R78" s="17" t="s">
-        <v>603</v>
+        <v>528</v>
       </c>
       <c r="S78" s="18"/>
       <c r="T78" s="18" t="s">
-        <v>996</v>
-      </c>
-      <c r="U78" s="28" t="s">
-        <v>997</v>
-      </c>
-      <c r="V78" s="28" t="s">
-        <v>998</v>
+        <v>873</v>
+      </c>
+      <c r="U78" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="V78" s="24" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>604</v>
+      <c r="A79" s="29">
+        <v>34720</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>605</v>
+        <v>529</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>606</v>
+        <v>530</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>607</v>
+        <v>531</v>
       </c>
       <c r="M79" s="12" t="s">
-        <v>607</v>
+        <v>531</v>
       </c>
       <c r="P79" s="15" t="s">
-        <v>608</v>
+        <v>532</v>
       </c>
       <c r="Q79" s="16" t="s">
-        <v>609</v>
+        <v>533</v>
       </c>
       <c r="R79" s="17" t="s">
-        <v>610</v>
+        <v>534</v>
       </c>
       <c r="S79" s="18"/>
       <c r="T79" s="18" t="s">
-        <v>999</v>
-      </c>
-      <c r="U79" s="28" t="s">
-        <v>1000</v>
+        <v>876</v>
+      </c>
+      <c r="U79" s="24" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>611</v>
+      <c r="A80" s="29">
+        <v>34722</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>612</v>
+        <v>535</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>613</v>
+        <v>536</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>614</v>
+        <v>537</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>615</v>
+        <v>538</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>616</v>
+        <v>539</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>617</v>
+        <v>540</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>618</v>
+        <v>541</v>
       </c>
       <c r="M80" s="12" t="s">
-        <v>618</v>
+        <v>541</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>619</v>
+        <v>542</v>
       </c>
       <c r="P80" s="15" t="s">
-        <v>620</v>
+        <v>543</v>
       </c>
       <c r="Q80" s="16" t="s">
-        <v>621</v>
+        <v>544</v>
       </c>
       <c r="T80" s="18" t="s">
-        <v>622</v>
+        <v>545</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>623</v>
+      <c r="A81" s="29">
+        <v>15723</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>624</v>
+        <v>546</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>625</v>
+        <v>547</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>626</v>
+        <v>548</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>627</v>
+        <v>549</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>628</v>
+        <v>550</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>629</v>
+        <v>551</v>
       </c>
       <c r="L81" s="18" t="s">
-        <v>630</v>
+        <v>552</v>
       </c>
       <c r="M81" s="12" t="s">
-        <v>630</v>
+        <v>552</v>
       </c>
       <c r="P81" s="15" t="s">
-        <v>631</v>
+        <v>553</v>
       </c>
       <c r="Q81" s="16" t="s">
-        <v>632</v>
+        <v>554</v>
       </c>
       <c r="R81" s="17" t="s">
-        <v>633</v>
+        <v>555</v>
       </c>
       <c r="S81" s="18"/>
       <c r="T81" s="18" t="s">
-        <v>634</v>
+        <v>556</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>635</v>
+      <c r="A82" s="29">
+        <v>25728</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>636</v>
+        <v>557</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>637</v>
+        <v>558</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>638</v>
+        <v>559</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>639</v>
+        <v>560</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>640</v>
+        <v>561</v>
       </c>
       <c r="L82" s="18" t="s">
-        <v>641</v>
+        <v>562</v>
       </c>
       <c r="M82" s="12" t="s">
-        <v>641</v>
+        <v>562</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>642</v>
+        <v>563</v>
       </c>
       <c r="P82" s="15" t="s">
-        <v>643</v>
+        <v>564</v>
       </c>
       <c r="Q82" s="16" t="s">
-        <v>644</v>
+        <v>565</v>
       </c>
       <c r="T82" s="18" t="s">
-        <v>645</v>
+        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>646</v>
+      <c r="A83" s="29">
+        <v>32734</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>647</v>
+        <v>567</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>648</v>
+        <v>568</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>649</v>
+        <v>569</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>650</v>
+        <v>570</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>651</v>
+        <v>571</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>652</v>
+        <v>572</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>653</v>
+        <v>573</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>654</v>
+        <v>574</v>
       </c>
       <c r="M83" s="12" t="s">
-        <v>654</v>
+        <v>574</v>
       </c>
       <c r="P83" s="15" t="s">
-        <v>655</v>
+        <v>575</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>656</v>
+        <v>576</v>
       </c>
       <c r="T83" s="18" t="s">
-        <v>1001</v>
-      </c>
-      <c r="U83" s="28" t="s">
-        <v>1002</v>
-      </c>
-      <c r="V83" s="28" t="s">
-        <v>1003</v>
+        <v>878</v>
+      </c>
+      <c r="U83" s="24" t="s">
+        <v>879</v>
+      </c>
+      <c r="V83" s="24" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>657</v>
+      <c r="A84" s="29">
+        <v>32735</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>658</v>
+        <v>577</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>659</v>
+        <v>578</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>660</v>
+        <v>579</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>661</v>
+        <v>580</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>662</v>
+        <v>581</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>663</v>
+        <v>582</v>
       </c>
       <c r="L84" s="18" t="s">
-        <v>664</v>
+        <v>583</v>
       </c>
       <c r="M84" s="12" t="s">
-        <v>664</v>
+        <v>583</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>665</v>
+        <v>584</v>
       </c>
       <c r="R84" s="17" t="s">
-        <v>666</v>
+        <v>585</v>
       </c>
       <c r="S84" s="18"/>
       <c r="T84" s="18" t="s">
-        <v>1004</v>
-      </c>
-      <c r="U84" s="28" t="s">
-        <v>1005</v>
-      </c>
-      <c r="V84" s="28" t="s">
-        <v>1006</v>
+        <v>881</v>
+      </c>
+      <c r="U84" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="V84" s="24" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>667</v>
+      <c r="A85" s="29">
+        <v>34739</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>668</v>
+        <v>586</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>669</v>
+        <v>587</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>670</v>
+        <v>588</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>671</v>
+        <v>589</v>
       </c>
       <c r="M85" s="12" t="s">
-        <v>671</v>
+        <v>589</v>
       </c>
       <c r="P85" s="15" t="s">
-        <v>672</v>
+        <v>590</v>
       </c>
       <c r="Q85" s="16" t="s">
-        <v>673</v>
+        <v>591</v>
       </c>
       <c r="R85" s="17" t="s">
-        <v>674</v>
+        <v>592</v>
       </c>
       <c r="S85" s="18"/>
       <c r="T85" s="18" t="s">
-        <v>675</v>
+        <v>593</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A86" s="21" t="s">
-        <v>676</v>
-      </c>
-      <c r="M86" s="22"/>
-      <c r="T86" s="22"/>
+      <c r="A86" s="30">
+        <v>37737</v>
+      </c>
+      <c r="M86" s="21"/>
+      <c r="T86" s="21"/>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>677</v>
+      <c r="A87" s="29">
+        <v>27762</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>678</v>
+        <v>594</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>679</v>
+        <v>595</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>680</v>
+        <v>596</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>681</v>
+        <v>597</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>682</v>
+        <v>598</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>683</v>
+        <v>599</v>
       </c>
       <c r="L87" s="18" t="s">
-        <v>684</v>
+        <v>600</v>
       </c>
       <c r="M87" s="12" t="s">
-        <v>684</v>
+        <v>600</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>685</v>
+        <v>601</v>
       </c>
       <c r="Q87" s="16" t="s">
-        <v>686</v>
+        <v>602</v>
       </c>
       <c r="R87" s="17" t="s">
-        <v>687</v>
+        <v>603</v>
       </c>
       <c r="S87" s="18"/>
       <c r="T87" s="18" t="s">
-        <v>1007</v>
-      </c>
-      <c r="U87" s="28" t="s">
-        <v>1008</v>
-      </c>
-      <c r="V87" s="28" t="s">
-        <v>1009</v>
+        <v>884</v>
+      </c>
+      <c r="U87" s="24" t="s">
+        <v>885</v>
+      </c>
+      <c r="V87" s="24" t="s">
+        <v>886</v>
       </c>
       <c r="W87">
         <v>9004417</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>688</v>
+      <c r="A88" s="29">
+        <v>30777</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>689</v>
+        <v>604</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>690</v>
+        <v>605</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>691</v>
+        <v>606</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>692</v>
+        <v>607</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>693</v>
+        <v>608</v>
       </c>
       <c r="L88" t="s">
-        <v>694</v>
+        <v>609</v>
       </c>
       <c r="M88" s="12" t="s">
-        <v>694</v>
+        <v>609</v>
       </c>
       <c r="R88" s="17" t="s">
-        <v>695</v>
+        <v>610</v>
       </c>
       <c r="S88" s="18"/>
       <c r="T88" s="18" t="s">
-        <v>1010</v>
-      </c>
-      <c r="U88" s="28" t="s">
-        <v>1011</v>
-      </c>
-      <c r="V88" s="28" t="s">
-        <v>1012</v>
+        <v>887</v>
+      </c>
+      <c r="U88" s="24" t="s">
+        <v>888</v>
+      </c>
+      <c r="V88" s="24" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>696</v>
+      <c r="A89" s="29">
+        <v>33783</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>697</v>
+        <v>611</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>698</v>
+        <v>612</v>
       </c>
       <c r="L89" t="s">
-        <v>699</v>
+        <v>613</v>
       </c>
       <c r="M89" s="12" t="s">
-        <v>699</v>
+        <v>613</v>
       </c>
       <c r="R89" s="17" t="s">
-        <v>700</v>
+        <v>614</v>
       </c>
       <c r="S89" s="18"/>
       <c r="T89" s="18" t="s">
-        <v>1013</v>
-      </c>
-      <c r="U89" s="28" t="s">
-        <v>1014</v>
+        <v>890</v>
+      </c>
+      <c r="U89" s="24" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>701</v>
+      <c r="A90" s="29">
+        <v>16789</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>702</v>
+        <v>615</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>703</v>
+        <v>616</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>704</v>
+        <v>617</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>705</v>
+        <v>618</v>
       </c>
       <c r="L90" s="18" t="s">
-        <v>706</v>
+        <v>619</v>
       </c>
       <c r="M90" s="12" t="s">
-        <v>706</v>
+        <v>619</v>
       </c>
       <c r="Q90" s="16" t="s">
-        <v>707</v>
+        <v>620</v>
       </c>
       <c r="R90" s="17" t="s">
-        <v>708</v>
+        <v>621</v>
       </c>
       <c r="S90" s="18"/>
       <c r="T90" s="18" t="s">
-        <v>1015</v>
-      </c>
-      <c r="U90" s="28" t="s">
-        <v>1016</v>
-      </c>
-      <c r="V90" s="28" t="s">
-        <v>1017</v>
+        <v>892</v>
+      </c>
+      <c r="U90" s="24" t="s">
+        <v>893</v>
+      </c>
+      <c r="V90" s="24" t="s">
+        <v>894</v>
       </c>
       <c r="W90">
         <v>5841129000</v>
@@ -7114,179 +6767,179 @@
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>709</v>
+      <c r="A91" s="29">
+        <v>16790</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>710</v>
+        <v>622</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>711</v>
+        <v>623</v>
       </c>
       <c r="L91" s="18" t="s">
-        <v>712</v>
+        <v>624</v>
       </c>
       <c r="M91" s="12" t="s">
-        <v>712</v>
+        <v>624</v>
       </c>
       <c r="Q91" s="16" t="s">
-        <v>713</v>
+        <v>625</v>
       </c>
       <c r="R91" s="17" t="s">
-        <v>714</v>
+        <v>626</v>
       </c>
       <c r="S91" s="18"/>
       <c r="T91" s="18" t="s">
-        <v>1018</v>
-      </c>
-      <c r="U91" s="28" t="s">
-        <v>1019</v>
-      </c>
-      <c r="V91" s="28" t="s">
-        <v>1020</v>
+        <v>895</v>
+      </c>
+      <c r="U91" s="24" t="s">
+        <v>896</v>
+      </c>
+      <c r="V91" s="24" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>715</v>
+      <c r="A92" s="29">
+        <v>42804</v>
       </c>
       <c r="L92" t="s">
-        <v>716</v>
+        <v>627</v>
       </c>
       <c r="M92" s="12" t="s">
-        <v>716</v>
+        <v>627</v>
       </c>
       <c r="Q92" s="16" t="s">
-        <v>717</v>
+        <v>628</v>
       </c>
       <c r="R92" s="17" t="s">
-        <v>718</v>
+        <v>629</v>
       </c>
       <c r="S92" s="18"/>
       <c r="T92" s="18" t="s">
-        <v>719</v>
+        <v>630</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>720</v>
+      <c r="A93" s="29">
+        <v>36815</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>721</v>
+        <v>631</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>722</v>
+        <v>632</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>723</v>
+        <v>633</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>724</v>
+        <v>634</v>
       </c>
       <c r="L93" s="18" t="s">
-        <v>725</v>
+        <v>635</v>
       </c>
       <c r="M93" s="12" t="s">
-        <v>725</v>
+        <v>635</v>
       </c>
       <c r="Q93" s="16" t="s">
-        <v>726</v>
+        <v>636</v>
       </c>
       <c r="R93" s="17" t="s">
-        <v>727</v>
+        <v>637</v>
       </c>
       <c r="S93" s="18"/>
       <c r="T93" s="18" t="s">
-        <v>728</v>
+        <v>638</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>729</v>
+      <c r="A94" s="29">
+        <v>30819</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>730</v>
+        <v>639</v>
       </c>
       <c r="L94" t="s">
-        <v>731</v>
+        <v>640</v>
       </c>
       <c r="M94" s="12" t="s">
-        <v>731</v>
+        <v>640</v>
       </c>
       <c r="Q94" s="16" t="s">
-        <v>732</v>
+        <v>641</v>
       </c>
       <c r="T94" s="18" t="s">
-        <v>1021</v>
-      </c>
-      <c r="U94" s="28" t="s">
-        <v>1022</v>
-      </c>
-      <c r="V94" s="28" t="s">
-        <v>1023</v>
+        <v>898</v>
+      </c>
+      <c r="U94" s="24" t="s">
+        <v>899</v>
+      </c>
+      <c r="V94" s="24" t="s">
+        <v>900</v>
       </c>
       <c r="W94">
         <v>7701463277</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>733</v>
+      <c r="A95" s="29">
+        <v>31820</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>734</v>
+        <v>642</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>735</v>
+        <v>643</v>
       </c>
       <c r="L95" s="18" t="s">
-        <v>736</v>
+        <v>644</v>
       </c>
       <c r="M95" s="12" t="s">
-        <v>736</v>
+        <v>644</v>
       </c>
       <c r="Q95" s="16" t="s">
-        <v>737</v>
+        <v>645</v>
       </c>
       <c r="R95" s="17" t="s">
-        <v>738</v>
+        <v>646</v>
       </c>
       <c r="S95" s="18"/>
       <c r="T95" s="18" t="s">
-        <v>739</v>
+        <v>647</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>740</v>
+      <c r="A96" s="29">
+        <v>33824</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>741</v>
+        <v>648</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>742</v>
+        <v>649</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>743</v>
+        <v>650</v>
       </c>
       <c r="L96" s="18" t="s">
-        <v>744</v>
+        <v>651</v>
       </c>
       <c r="M96" s="12" t="s">
-        <v>744</v>
+        <v>651</v>
       </c>
       <c r="R96" s="17" t="s">
-        <v>745</v>
+        <v>652</v>
       </c>
       <c r="S96" s="18"/>
       <c r="T96" s="18" t="s">
-        <v>1024</v>
-      </c>
-      <c r="U96" s="28" t="s">
-        <v>1025</v>
-      </c>
-      <c r="V96" s="28" t="s">
-        <v>1026</v>
+        <v>901</v>
+      </c>
+      <c r="U96" s="24" t="s">
+        <v>902</v>
+      </c>
+      <c r="V96" s="24" t="s">
+        <v>903</v>
       </c>
       <c r="W96">
         <v>51900802</v>
@@ -7299,218 +6952,218 @@
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>746</v>
+      <c r="A97" s="29">
+        <v>29825</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>747</v>
+        <v>653</v>
       </c>
       <c r="L97" t="s">
-        <v>748</v>
+        <v>654</v>
       </c>
       <c r="M97" s="12" t="s">
-        <v>748</v>
+        <v>654</v>
       </c>
       <c r="R97" s="17" t="s">
-        <v>749</v>
+        <v>655</v>
       </c>
       <c r="S97" s="18"/>
       <c r="T97" s="18" t="s">
-        <v>1027</v>
-      </c>
-      <c r="U97" s="28" t="s">
-        <v>1028</v>
-      </c>
-      <c r="V97" s="28" t="s">
-        <v>1029</v>
+        <v>904</v>
+      </c>
+      <c r="U97" s="24" t="s">
+        <v>905</v>
+      </c>
+      <c r="V97" s="24" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>750</v>
+      <c r="A98" s="29">
+        <v>29826</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>751</v>
+        <v>656</v>
       </c>
       <c r="L98" s="18" t="s">
-        <v>752</v>
+        <v>657</v>
       </c>
       <c r="M98" s="12" t="s">
-        <v>752</v>
+        <v>657</v>
       </c>
       <c r="R98" s="17" t="s">
-        <v>753</v>
+        <v>658</v>
       </c>
       <c r="S98" s="18"/>
       <c r="T98" s="18" t="s">
-        <v>1030</v>
-      </c>
-      <c r="U98" s="28" t="s">
-        <v>1031</v>
-      </c>
-      <c r="V98" s="28" t="s">
-        <v>1032</v>
+        <v>907</v>
+      </c>
+      <c r="U98" s="24" t="s">
+        <v>908</v>
+      </c>
+      <c r="V98" s="24" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>754</v>
+      <c r="A99" s="29">
+        <v>33827</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>755</v>
+        <v>659</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>756</v>
+        <v>660</v>
       </c>
       <c r="L99" s="18" t="s">
-        <v>757</v>
+        <v>661</v>
       </c>
       <c r="M99" s="12" t="s">
-        <v>757</v>
+        <v>661</v>
       </c>
       <c r="O99" s="14" t="s">
-        <v>758</v>
+        <v>662</v>
       </c>
       <c r="T99" s="18" t="s">
-        <v>759</v>
+        <v>663</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>760</v>
+      <c r="A100" s="29">
+        <v>18911</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>761</v>
+        <v>664</v>
       </c>
       <c r="L100" s="18" t="s">
-        <v>762</v>
+        <v>665</v>
       </c>
       <c r="M100" s="12" t="s">
-        <v>762</v>
+        <v>665</v>
       </c>
       <c r="P100" s="15" t="s">
-        <v>763</v>
+        <v>666</v>
       </c>
       <c r="T100" s="18" t="s">
-        <v>1033</v>
-      </c>
-      <c r="U100" s="28" t="s">
-        <v>1034</v>
+        <v>910</v>
+      </c>
+      <c r="U100" s="24" t="s">
+        <v>911</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>764</v>
+      <c r="A101" s="29">
+        <v>33976</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>765</v>
+        <v>667</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>766</v>
+        <v>668</v>
       </c>
       <c r="L101" s="18" t="s">
-        <v>767</v>
+        <v>669</v>
       </c>
       <c r="M101" s="12" t="s">
-        <v>767</v>
+        <v>669</v>
       </c>
       <c r="R101" s="17" t="s">
-        <v>768</v>
+        <v>670</v>
       </c>
       <c r="S101" s="18"/>
       <c r="T101" s="18" t="s">
-        <v>1035</v>
-      </c>
-      <c r="U101" s="28" t="s">
-        <v>1036</v>
-      </c>
-      <c r="V101" s="28" t="s">
-        <v>1037</v>
+        <v>912</v>
+      </c>
+      <c r="U101" s="24" t="s">
+        <v>913</v>
+      </c>
+      <c r="V101" s="24" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>769</v>
+      <c r="A102" s="29">
+        <v>33987</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>770</v>
+        <v>671</v>
       </c>
       <c r="T102" s="18" t="s">
-        <v>1038</v>
-      </c>
-      <c r="U102" s="28" t="s">
-        <v>1039</v>
+        <v>915</v>
+      </c>
+      <c r="U102" s="24" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>771</v>
+      <c r="A103" s="29">
+        <v>28988</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>772</v>
+        <v>672</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>773</v>
+        <v>673</v>
       </c>
       <c r="R103" s="17" t="s">
-        <v>774</v>
+        <v>674</v>
       </c>
       <c r="S103" s="18"/>
       <c r="T103" s="18" t="s">
-        <v>1040</v>
-      </c>
-      <c r="U103" s="28" t="s">
-        <v>1041</v>
-      </c>
-      <c r="V103" s="28" t="s">
-        <v>1042</v>
+        <v>917</v>
+      </c>
+      <c r="U103" s="24" t="s">
+        <v>918</v>
+      </c>
+      <c r="V103" s="24" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A104" s="21" t="s">
-        <v>775</v>
-      </c>
-      <c r="M104" s="22"/>
-      <c r="T104" s="21" t="s">
-        <v>907</v>
-      </c>
-      <c r="U104" s="28" t="s">
-        <v>908</v>
+      <c r="A104" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="M104" s="21"/>
+      <c r="T104" s="20" t="s">
+        <v>784</v>
+      </c>
+      <c r="U104" s="24" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>776</v>
+      <c r="A105" s="29">
+        <v>33992</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>777</v>
+        <v>676</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>441</v>
+        <v>386</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>778</v>
+        <v>677</v>
       </c>
       <c r="L105" s="18" t="s">
-        <v>779</v>
-      </c>
-      <c r="M105" s="20" t="s">
-        <v>779</v>
+        <v>678</v>
+      </c>
+      <c r="M105" s="19" t="s">
+        <v>678</v>
       </c>
       <c r="O105" s="14" t="s">
-        <v>780</v>
+        <v>679</v>
       </c>
       <c r="T105" s="18" t="s">
-        <v>1043</v>
-      </c>
-      <c r="U105" s="28" t="s">
-        <v>1044</v>
-      </c>
-      <c r="V105" s="28" t="s">
-        <v>1045</v>
+        <v>920</v>
+      </c>
+      <c r="U105" s="24" t="s">
+        <v>921</v>
+      </c>
+      <c r="V105" s="24" t="s">
+        <v>922</v>
       </c>
       <c r="W105">
         <v>52015297</v>
@@ -7523,406 +7176,406 @@
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>781</v>
+      <c r="A106" s="29">
+        <v>30997</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>782</v>
+        <v>680</v>
       </c>
       <c r="L106" s="18" t="s">
-        <v>783</v>
+        <v>681</v>
       </c>
       <c r="M106" s="12" t="s">
-        <v>783</v>
+        <v>681</v>
       </c>
       <c r="T106" s="18" t="s">
-        <v>1046</v>
-      </c>
-      <c r="U106" s="28" t="s">
-        <v>1047</v>
-      </c>
-      <c r="V106" s="28" t="s">
-        <v>1048</v>
+        <v>923</v>
+      </c>
+      <c r="U106" s="24" t="s">
+        <v>924</v>
+      </c>
+      <c r="V106" s="24" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>784</v>
+      <c r="A107" s="29">
+        <v>161065</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>841</v>
+        <v>718</v>
       </c>
       <c r="L107" t="s">
-        <v>785</v>
-      </c>
-      <c r="M107" s="21"/>
+        <v>682</v>
+      </c>
+      <c r="M107" s="20"/>
       <c r="T107" s="18" t="s">
-        <v>1049</v>
-      </c>
-      <c r="U107" s="28" t="s">
-        <v>1050</v>
+        <v>926</v>
+      </c>
+      <c r="U107" s="24" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>786</v>
+      <c r="A108" s="29">
+        <v>291066</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>787</v>
+        <v>683</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>788</v>
+        <v>684</v>
       </c>
       <c r="L108" s="18" t="s">
-        <v>789</v>
+        <v>685</v>
       </c>
       <c r="M108" s="12" t="s">
-        <v>789</v>
+        <v>685</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>790</v>
+        <v>686</v>
       </c>
       <c r="T108" s="18" t="s">
-        <v>791</v>
+        <v>687</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A109" s="21" t="s">
-        <v>792</v>
-      </c>
-      <c r="T109" s="21" t="s">
-        <v>1051</v>
-      </c>
-      <c r="U109" s="28" t="s">
-        <v>1052</v>
+      <c r="A109" s="30">
+        <v>63999</v>
+      </c>
+      <c r="T109" s="20" t="s">
+        <v>928</v>
+      </c>
+      <c r="U109" s="24" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A110" s="21" t="s">
-        <v>794</v>
-      </c>
-      <c r="T110" s="21" t="s">
-        <v>795</v>
+      <c r="A110" s="30">
+        <v>251070</v>
+      </c>
+      <c r="T110" s="20" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A111" s="21" t="s">
-        <v>796</v>
-      </c>
-      <c r="T111" s="21" t="s">
-        <v>1053</v>
-      </c>
-      <c r="U111" s="28" t="s">
-        <v>1054</v>
+      <c r="A111" s="30">
+        <v>401071</v>
+      </c>
+      <c r="T111" s="20" t="s">
+        <v>930</v>
+      </c>
+      <c r="U111" s="24" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A112" s="21" t="s">
-        <v>798</v>
-      </c>
-      <c r="T112" s="21" t="s">
-        <v>799</v>
+      <c r="A112" s="30">
+        <v>401072</v>
+      </c>
+      <c r="T112" s="20" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A113" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="T113" s="21" t="s">
-        <v>1055</v>
-      </c>
-      <c r="U113" s="28" t="s">
-        <v>1056</v>
+      <c r="A113" s="30">
+        <v>401073</v>
+      </c>
+      <c r="T113" s="20" t="s">
+        <v>932</v>
+      </c>
+      <c r="U113" s="24" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>802</v>
+      <c r="A114" s="29">
+        <v>341074</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>803</v>
+        <v>693</v>
       </c>
       <c r="T114" s="18" t="s">
-        <v>1057</v>
-      </c>
-      <c r="U114" s="28" t="s">
-        <v>1058</v>
+        <v>934</v>
+      </c>
+      <c r="U114" s="24" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>804</v>
+      <c r="A115" s="29">
+        <v>251075</v>
       </c>
       <c r="K115" s="11" t="s">
-        <v>805</v>
+        <v>694</v>
       </c>
       <c r="L115" s="18" t="s">
-        <v>806</v>
+        <v>695</v>
       </c>
       <c r="M115" s="12" t="s">
-        <v>806</v>
+        <v>695</v>
       </c>
       <c r="T115" s="18" t="s">
-        <v>807</v>
+        <v>696</v>
       </c>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>808</v>
+      <c r="A116" s="29">
+        <v>321081</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>809</v>
+        <v>697</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>810</v>
+        <v>698</v>
       </c>
       <c r="R116" s="17" t="s">
-        <v>811</v>
+        <v>699</v>
       </c>
       <c r="S116" s="18"/>
       <c r="T116" s="18" t="s">
-        <v>1059</v>
-      </c>
-      <c r="U116" s="28" t="s">
-        <v>1060</v>
-      </c>
-      <c r="V116" s="28" t="s">
-        <v>1061</v>
+        <v>936</v>
+      </c>
+      <c r="U116" s="24" t="s">
+        <v>937</v>
+      </c>
+      <c r="V116" s="24" t="s">
+        <v>938</v>
       </c>
       <c r="W116" t="s">
-        <v>1062</v>
+        <v>939</v>
       </c>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>812</v>
+      <c r="A117" s="29">
+        <v>191082</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>813</v>
+        <v>700</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>814</v>
+        <v>701</v>
       </c>
       <c r="L117" t="s">
-        <v>815</v>
+        <v>702</v>
       </c>
       <c r="M117" s="12" t="s">
-        <v>815</v>
+        <v>702</v>
       </c>
       <c r="R117" s="17" t="s">
-        <v>816</v>
+        <v>703</v>
       </c>
       <c r="S117" s="18"/>
       <c r="T117" s="18" t="s">
-        <v>1063</v>
-      </c>
-      <c r="U117" s="28" t="s">
-        <v>1064</v>
-      </c>
-      <c r="V117" s="28" t="s">
-        <v>1065</v>
+        <v>940</v>
+      </c>
+      <c r="U117" s="24" t="s">
+        <v>941</v>
+      </c>
+      <c r="V117" s="24" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="S118" s="23" t="s">
-        <v>847</v>
+      <c r="A118" s="29">
+        <v>341083</v>
+      </c>
+      <c r="S118" s="22" t="s">
+        <v>724</v>
       </c>
       <c r="T118" s="18" t="s">
-        <v>818</v>
+        <v>704</v>
       </c>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="S119" s="23" t="s">
-        <v>848</v>
+      <c r="A119" s="29">
+        <v>341084</v>
+      </c>
+      <c r="S119" s="22" t="s">
+        <v>725</v>
       </c>
       <c r="T119" s="18" t="s">
-        <v>1066</v>
-      </c>
-      <c r="U119" s="28" t="s">
-        <v>1067</v>
+        <v>943</v>
+      </c>
+      <c r="U119" s="24" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>820</v>
+      <c r="A120" s="29">
+        <v>131085</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>821</v>
+        <v>705</v>
       </c>
       <c r="L120" t="s">
-        <v>822</v>
+        <v>706</v>
       </c>
       <c r="M120" s="12" t="s">
-        <v>822</v>
+        <v>706</v>
       </c>
       <c r="Q120" s="16" t="s">
-        <v>823</v>
+        <v>707</v>
       </c>
       <c r="T120" s="18" t="s">
-        <v>1068</v>
-      </c>
-      <c r="U120" s="28" t="s">
-        <v>1069</v>
-      </c>
-      <c r="V120" s="28" t="s">
-        <v>1070</v>
+        <v>945</v>
+      </c>
+      <c r="U120" s="24" t="s">
+        <v>946</v>
+      </c>
+      <c r="V120" s="24" t="s">
+        <v>947</v>
       </c>
       <c r="W120" t="s">
-        <v>1071</v>
+        <v>948</v>
       </c>
       <c r="X120" t="s">
-        <v>1072</v>
+        <v>949</v>
       </c>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>824</v>
+      <c r="A121" s="29">
+        <v>131086</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>825</v>
+        <v>708</v>
       </c>
       <c r="L121" s="18" t="s">
-        <v>826</v>
+        <v>709</v>
       </c>
       <c r="M121" s="12" t="s">
-        <v>826</v>
+        <v>709</v>
       </c>
       <c r="T121" s="18" t="s">
-        <v>1073</v>
-      </c>
-      <c r="U121" s="28" t="s">
-        <v>1074</v>
-      </c>
-      <c r="V121" s="28" t="s">
-        <v>1075</v>
+        <v>950</v>
+      </c>
+      <c r="U121" s="24" t="s">
+        <v>951</v>
+      </c>
+      <c r="V121" s="24" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>827</v>
+      <c r="A122" s="29">
+        <v>341087</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>828</v>
+        <v>710</v>
       </c>
       <c r="T122" s="18" t="s">
-        <v>1076</v>
-      </c>
-      <c r="U122" s="28" t="s">
-        <v>1077</v>
-      </c>
-      <c r="V122" s="28" t="s">
-        <v>1078</v>
+        <v>953</v>
+      </c>
+      <c r="U122" s="24" t="s">
+        <v>954</v>
+      </c>
+      <c r="V122" s="24" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A123" s="21" t="s">
-        <v>829</v>
-      </c>
-      <c r="T123" s="22"/>
+      <c r="A123" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="T123" s="21"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A124" s="21" t="s">
-        <v>830</v>
-      </c>
-      <c r="T124" s="21" t="s">
-        <v>795</v>
+      <c r="A124" s="30">
+        <v>251088</v>
+      </c>
+      <c r="T124" s="20" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="R125" s="23">
+      <c r="A125" s="29">
+        <v>511089</v>
+      </c>
+      <c r="R125" s="22">
         <v>94036400</v>
       </c>
       <c r="T125" s="18" t="s">
-        <v>1079</v>
-      </c>
-      <c r="U125" s="28" t="s">
-        <v>1080</v>
-      </c>
-      <c r="V125" s="28" t="s">
-        <v>1081</v>
+        <v>956</v>
+      </c>
+      <c r="U125" s="24" t="s">
+        <v>957</v>
+      </c>
+      <c r="V125" s="24" t="s">
+        <v>958</v>
       </c>
       <c r="W125" t="s">
-        <v>1082</v>
+        <v>959</v>
       </c>
       <c r="X125" t="s">
-        <v>1083</v>
+        <v>960</v>
       </c>
       <c r="Y125" t="s">
-        <v>1080</v>
+        <v>957</v>
       </c>
       <c r="Z125" t="s">
-        <v>1084</v>
+        <v>961</v>
       </c>
       <c r="AA125" t="s">
-        <v>1082</v>
+        <v>959</v>
       </c>
       <c r="AB125" t="s">
-        <v>1083</v>
+        <v>960</v>
       </c>
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B126" s="23" t="s">
-        <v>850</v>
+      <c r="A126" s="29">
+        <v>261090</v>
+      </c>
+      <c r="B126" s="22" t="s">
+        <v>727</v>
       </c>
       <c r="T126" s="18" t="s">
-        <v>1085</v>
-      </c>
-      <c r="U126" s="28" t="s">
-        <v>1086</v>
-      </c>
-      <c r="V126" s="28" t="s">
-        <v>1087</v>
+        <v>962</v>
+      </c>
+      <c r="U126" s="24" t="s">
+        <v>963</v>
+      </c>
+      <c r="V126" s="24" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>833</v>
+      <c r="A127" s="29">
+        <v>261091</v>
       </c>
       <c r="R127" s="17" t="s">
-        <v>834</v>
+        <v>712</v>
       </c>
       <c r="S127" s="18"/>
       <c r="T127" s="18" t="s">
-        <v>1088</v>
-      </c>
-      <c r="U127" s="28" t="s">
-        <v>1089</v>
-      </c>
-      <c r="V127" s="28" t="s">
-        <v>1090</v>
+        <v>965</v>
+      </c>
+      <c r="U127" s="24" t="s">
+        <v>966</v>
+      </c>
+      <c r="V127" s="24" t="s">
+        <v>967</v>
       </c>
       <c r="W127" t="s">
-        <v>1091</v>
+        <v>968</v>
       </c>
       <c r="X127" t="s">
-        <v>1092</v>
+        <v>969</v>
       </c>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
-        <v>835</v>
+      <c r="A128" s="29">
+        <v>341092</v>
       </c>
       <c r="R128" s="17" t="s">
-        <v>836</v>
+        <v>713</v>
       </c>
       <c r="S128" s="18"/>
       <c r="T128" s="18" t="s">
-        <v>1093</v>
-      </c>
-      <c r="U128" s="28" t="s">
-        <v>1094</v>
+        <v>970</v>
+      </c>
+      <c r="U128" s="24" t="s">
+        <v>971</v>
       </c>
     </row>
   </sheetData>
@@ -7936,142 +7589,214 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C81E66E-DB0B-4CD3-9F7E-BD3F14DE7413}">
   <sheetPr codeName="Sayfa2"/>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="19"/>
-    <col min="2" max="2" width="26.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="8.88671875" style="28"/>
+    <col min="2" max="2" width="33.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="24" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>838</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>851</v>
+    <row r="1" spans="1:2" s="25" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="25">
+      <c r="A2" s="26">
         <v>13275</v>
       </c>
-      <c r="B2" s="25">
-        <v>43860</v>
+      <c r="B2" s="27" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+      <c r="A3" s="26">
         <v>13278</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>39</v>
+      <c r="B3" s="27" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="26">
         <v>13284</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>79</v>
+      <c r="B4" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="26">
         <v>45387</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>245</v>
+      <c r="B5" s="27" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="26">
         <v>45396</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>248</v>
+      <c r="B6" s="27" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="25">
-        <v>2952956</v>
+        <v>228</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
+        <v>28431</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
         <v>45473</v>
       </c>
-      <c r="B8" s="26"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="B9" s="27"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>59480</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="26">
+        <v>59519</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
+        <v>16704</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
         <v>37737</v>
       </c>
-      <c r="B9" s="26"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
-        <v>775</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
+      <c r="B13" s="27"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="26">
+        <v>18911</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="26" t="s">
+        <v>675</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="26">
+        <v>30997</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="26">
+        <v>291066</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="26">
         <v>63999</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+      <c r="B18" s="27" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="26">
         <v>251070</v>
       </c>
-      <c r="B12" s="26" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+      <c r="B19" s="27" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="26">
         <v>401071</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
+      <c r="B20" s="27" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="26">
         <v>401072</v>
       </c>
-      <c r="B14" s="25">
-        <v>8941010571</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="25">
+      <c r="B21" s="27" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="26">
         <v>401073</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>829</v>
-      </c>
-      <c r="B16" s="26"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+      <c r="B22" s="27" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="26">
+        <v>251075</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="26">
+        <v>131086</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
+        <v>711</v>
+      </c>
+      <c r="B25" s="27"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="26">
         <v>251088</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>795</v>
+      <c r="B26" s="27" t="s">
+        <v>689</v>
       </c>
     </row>
   </sheetData>
